--- a/research/traditional_assets/database/data/finland/finland_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_retail_grocery_and_food.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07213490275057305</v>
+        <v>0.0720266329450719</v>
       </c>
       <c r="C2">
-        <v>10092.25684710421</v>
+        <v>10023.72643709214</v>
       </c>
       <c r="D2">
-        <v>9846.956847104208</v>
+        <v>9887.607437092141</v>
       </c>
       <c r="E2">
-        <v>-3443.6</v>
+        <v>-3334.419</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>109.181</v>
       </c>
       <c r="G2">
         <v>245.3</v>
@@ -1457,28 +1457,28 @@
         <v>246.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.4918043</v>
       </c>
       <c r="N2">
-        <v>246.5</v>
+        <v>241.0081957</v>
       </c>
       <c r="O2">
-        <v>49.3</v>
+        <v>48.20163914</v>
       </c>
       <c r="P2">
-        <v>197.2</v>
+        <v>192.80655656</v>
       </c>
       <c r="Q2">
-        <v>834.3</v>
+        <v>829.90655656</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07213490275057305</v>
+        <v>0.07234771004552717</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5458488604849997</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>44.88506627958319</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0720266329450719</v>
+        <v>0.07191836313957076</v>
       </c>
       <c r="C3">
-        <v>10023.72643709214</v>
+        <v>9955.53304907858</v>
       </c>
       <c r="D3">
-        <v>9887.607437092141</v>
+        <v>9928.59504907858</v>
       </c>
       <c r="E3">
-        <v>-3334.419</v>
+        <v>-3225.238</v>
       </c>
       <c r="F3">
-        <v>109.181</v>
+        <v>218.362</v>
       </c>
       <c r="G3">
         <v>245.3</v>
@@ -1539,28 +1539,28 @@
         <v>246.5</v>
       </c>
       <c r="M3">
-        <v>5.4918043</v>
+        <v>10.9836086</v>
       </c>
       <c r="N3">
-        <v>241.0081957</v>
+        <v>235.5163914</v>
       </c>
       <c r="O3">
-        <v>48.20163914</v>
+        <v>47.10327828</v>
       </c>
       <c r="P3">
-        <v>192.80655656</v>
+        <v>188.41311312</v>
       </c>
       <c r="Q3">
-        <v>829.90655656</v>
+        <v>825.5131131200001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07234771004552717</v>
+        <v>0.07256486034650078</v>
       </c>
       <c r="T3">
-        <v>0.5458488604849997</v>
+        <v>0.5503136992276687</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>44.88506627958319</v>
+        <v>22.4425331397916</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07191836313957076</v>
+        <v>0.07181009333406962</v>
       </c>
       <c r="C4">
-        <v>9955.53304907858</v>
+        <v>9887.680891734255</v>
       </c>
       <c r="D4">
-        <v>9928.59504907858</v>
+        <v>9969.923891734255</v>
       </c>
       <c r="E4">
-        <v>-3225.238</v>
+        <v>-3116.057</v>
       </c>
       <c r="F4">
-        <v>218.362</v>
+        <v>327.543</v>
       </c>
       <c r="G4">
         <v>245.3</v>
@@ -1621,28 +1621,28 @@
         <v>246.5</v>
       </c>
       <c r="M4">
-        <v>10.9836086</v>
+        <v>16.4754129</v>
       </c>
       <c r="N4">
-        <v>235.5163914</v>
+        <v>230.0245871</v>
       </c>
       <c r="O4">
-        <v>47.10327828</v>
+        <v>46.00491742</v>
       </c>
       <c r="P4">
-        <v>188.41311312</v>
+        <v>184.01966968</v>
       </c>
       <c r="Q4">
-        <v>825.5131131200001</v>
+        <v>821.11966968</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07256486034650078</v>
+        <v>0.07278648797326764</v>
       </c>
       <c r="T4">
-        <v>0.5503136992276687</v>
+        <v>0.5548705965011144</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>22.4425331397916</v>
+        <v>14.96168875986107</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07181009333406962</v>
+        <v>0.07170182352856848</v>
       </c>
       <c r="C5">
-        <v>9887.680891734255</v>
+        <v>9820.174244099011</v>
       </c>
       <c r="D5">
-        <v>9969.923891734255</v>
+        <v>10011.59824409901</v>
       </c>
       <c r="E5">
-        <v>-3116.057</v>
+        <v>-3006.876</v>
       </c>
       <c r="F5">
-        <v>327.543</v>
+        <v>436.724</v>
       </c>
       <c r="G5">
         <v>245.3</v>
@@ -1703,28 +1703,28 @@
         <v>246.5</v>
       </c>
       <c r="M5">
-        <v>16.4754129</v>
+        <v>21.9672172</v>
       </c>
       <c r="N5">
-        <v>230.0245871</v>
+        <v>224.5327828</v>
       </c>
       <c r="O5">
-        <v>46.00491742</v>
+        <v>44.90655656000001</v>
       </c>
       <c r="P5">
-        <v>184.01966968</v>
+        <v>179.62622624</v>
       </c>
       <c r="Q5">
-        <v>821.11966968</v>
+        <v>816.72622624</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07278648797326764</v>
+        <v>0.07301273284225883</v>
       </c>
       <c r="T5">
-        <v>0.5548705965011144</v>
+        <v>0.5595224291344236</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>14.96168875986107</v>
+        <v>11.2212665698958</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07170182352856848</v>
+        <v>0.07159355372306732</v>
       </c>
       <c r="C6">
-        <v>9820.174244099011</v>
+        <v>9753.017457058662</v>
       </c>
       <c r="D6">
-        <v>10011.59824409901</v>
+        <v>10053.62245705866</v>
       </c>
       <c r="E6">
-        <v>-3006.876</v>
+        <v>-2897.695</v>
       </c>
       <c r="F6">
-        <v>436.724</v>
+        <v>545.9050000000001</v>
       </c>
       <c r="G6">
         <v>245.3</v>
@@ -1785,28 +1785,28 @@
         <v>246.5</v>
       </c>
       <c r="M6">
-        <v>21.9672172</v>
+        <v>27.4590215</v>
       </c>
       <c r="N6">
-        <v>224.5327828</v>
+        <v>219.0409785</v>
       </c>
       <c r="O6">
-        <v>44.90655656000001</v>
+        <v>43.8081957</v>
       </c>
       <c r="P6">
-        <v>179.62622624</v>
+        <v>175.2327828</v>
       </c>
       <c r="Q6">
-        <v>816.72622624</v>
+        <v>812.3327828</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07301273284225883</v>
+        <v>0.0732437407611235</v>
       </c>
       <c r="T6">
-        <v>0.5595224291344236</v>
+        <v>0.5642721950863286</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>11.2212665698958</v>
+        <v>8.977013255916638</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07159355372306732</v>
+        <v>0.07155728391756618</v>
       </c>
       <c r="C7">
-        <v>9753.017457058662</v>
+        <v>9657.993343020182</v>
       </c>
       <c r="D7">
-        <v>10053.62245705866</v>
+        <v>10067.77934302018</v>
       </c>
       <c r="E7">
-        <v>-2897.695</v>
+        <v>-2788.514</v>
       </c>
       <c r="F7">
-        <v>545.9050000000001</v>
+        <v>655.0860000000001</v>
       </c>
       <c r="G7">
         <v>245.3</v>
@@ -1867,45 +1867,45 @@
         <v>246.5</v>
       </c>
       <c r="M7">
-        <v>27.4590215</v>
+        <v>33.93345480000001</v>
       </c>
       <c r="N7">
-        <v>219.0409785</v>
+        <v>212.5665452</v>
       </c>
       <c r="O7">
-        <v>43.8081957</v>
+        <v>42.51330904</v>
       </c>
       <c r="P7">
-        <v>175.2327828</v>
+        <v>170.05323616</v>
       </c>
       <c r="Q7">
-        <v>812.3327828</v>
+        <v>807.15323616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0732437407611235</v>
+        <v>0.07347966374209168</v>
       </c>
       <c r="T7">
-        <v>0.5642721950863286</v>
+        <v>0.5691230198882743</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.977013255916638</v>
+        <v>7.264217612171925</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07155728391756618</v>
+        <v>0.07155621411206503</v>
       </c>
       <c r="C8">
-        <v>9657.993343020182</v>
+        <v>9549.230516501681</v>
       </c>
       <c r="D8">
-        <v>10067.77934302018</v>
+        <v>10068.19751650168</v>
       </c>
       <c r="E8">
-        <v>-2788.514</v>
+        <v>-2679.333</v>
       </c>
       <c r="F8">
-        <v>655.086</v>
+        <v>764.2669999999999</v>
       </c>
       <c r="G8">
         <v>245.3</v>
@@ -1949,45 +1949,45 @@
         <v>246.5</v>
       </c>
       <c r="M8">
-        <v>33.9334548</v>
+        <v>40.8882845</v>
       </c>
       <c r="N8">
-        <v>212.5665452</v>
+        <v>205.6117155</v>
       </c>
       <c r="O8">
-        <v>42.51330904</v>
+        <v>41.1223431</v>
       </c>
       <c r="P8">
-        <v>170.05323616</v>
+        <v>164.4893724</v>
       </c>
       <c r="Q8">
-        <v>807.15323616</v>
+        <v>801.5893724</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07347966374209168</v>
+        <v>0.0737206603355538</v>
       </c>
       <c r="T8">
-        <v>0.5691230198882743</v>
+        <v>0.5740781635031651</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.264217612171927</v>
+        <v>6.028621719260441</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07155621411206503</v>
+        <v>0.07152474430656387</v>
       </c>
       <c r="C9">
-        <v>9549.230516501681</v>
+        <v>9452.366226585002</v>
       </c>
       <c r="D9">
-        <v>10068.19751650168</v>
+        <v>10080.514226585</v>
       </c>
       <c r="E9">
-        <v>-2679.333</v>
+        <v>-2570.152</v>
       </c>
       <c r="F9">
-        <v>764.2670000000001</v>
+        <v>873.4480000000001</v>
       </c>
       <c r="G9">
         <v>245.3</v>
@@ -2031,45 +2031,45 @@
         <v>246.5</v>
       </c>
       <c r="M9">
-        <v>40.8882845</v>
+        <v>47.42822640000001</v>
       </c>
       <c r="N9">
-        <v>205.6117155</v>
+        <v>199.0717736</v>
       </c>
       <c r="O9">
-        <v>41.1223431</v>
+        <v>39.81435472</v>
       </c>
       <c r="P9">
-        <v>164.4893724</v>
+        <v>159.25741888</v>
       </c>
       <c r="Q9">
-        <v>801.5893724</v>
+        <v>796.3574188800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0737206603355538</v>
+        <v>0.07396689598539552</v>
       </c>
       <c r="T9">
-        <v>0.5740781635031651</v>
+        <v>0.5791410276314229</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.02862171926044</v>
+        <v>5.19732696561472</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07152474430656387</v>
+        <v>0.07144847450106274</v>
       </c>
       <c r="C10">
-        <v>9452.366226585002</v>
+        <v>9373.16123390587</v>
       </c>
       <c r="D10">
-        <v>10080.514226585</v>
+        <v>10110.49023390587</v>
       </c>
       <c r="E10">
-        <v>-2570.152</v>
+        <v>-2460.971</v>
       </c>
       <c r="F10">
-        <v>873.4480000000001</v>
+        <v>982.629</v>
       </c>
       <c r="G10">
         <v>245.3</v>
@@ -2113,28 +2113,28 @@
         <v>246.5</v>
       </c>
       <c r="M10">
-        <v>47.42822640000001</v>
+        <v>53.3567547</v>
       </c>
       <c r="N10">
-        <v>199.0717736</v>
+        <v>193.1432453</v>
       </c>
       <c r="O10">
-        <v>39.81435472</v>
+        <v>38.62864906</v>
       </c>
       <c r="P10">
-        <v>159.25741888</v>
+        <v>154.51459624</v>
       </c>
       <c r="Q10">
-        <v>796.3574188800001</v>
+        <v>791.6145962400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07396689598539552</v>
+        <v>0.07421854340776125</v>
       </c>
       <c r="T10">
-        <v>0.5791410276314229</v>
+        <v>0.5843151634987634</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.19732696561472</v>
+        <v>4.61984619165753</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07144847450106274</v>
+        <v>0.07145220469556159</v>
       </c>
       <c r="C11">
-        <v>9373.16123390587</v>
+        <v>9262.510025185074</v>
       </c>
       <c r="D11">
-        <v>10110.49023390587</v>
+        <v>10109.02002518507</v>
       </c>
       <c r="E11">
-        <v>-2460.971</v>
+        <v>-2351.79</v>
       </c>
       <c r="F11">
-        <v>982.629</v>
+        <v>1091.81</v>
       </c>
       <c r="G11">
         <v>245.3</v>
@@ -2195,45 +2195,45 @@
         <v>246.5</v>
       </c>
       <c r="M11">
-        <v>53.3567547</v>
+        <v>60.377093</v>
       </c>
       <c r="N11">
-        <v>193.1432453</v>
+        <v>186.122907</v>
       </c>
       <c r="O11">
-        <v>38.62864906</v>
+        <v>37.2245814</v>
       </c>
       <c r="P11">
-        <v>154.51459624</v>
+        <v>148.8983256</v>
       </c>
       <c r="Q11">
-        <v>791.6145962400001</v>
+        <v>785.9983256</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07421854340776125</v>
+        <v>0.07447578299506843</v>
       </c>
       <c r="T11">
-        <v>0.5843151634987634</v>
+        <v>0.5896042801631559</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.61984619165753</v>
+        <v>4.082674202283968</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07145220469556159</v>
+        <v>0.07138393489006045</v>
       </c>
       <c r="C12">
-        <v>9262.510025185074</v>
+        <v>9180.30457972319</v>
       </c>
       <c r="D12">
-        <v>10109.02002518507</v>
+        <v>10135.99557972319</v>
       </c>
       <c r="E12">
-        <v>-2351.79</v>
+        <v>-2242.609</v>
       </c>
       <c r="F12">
-        <v>1091.81</v>
+        <v>1200.991</v>
       </c>
       <c r="G12">
         <v>245.3</v>
@@ -2277,28 +2277,28 @@
         <v>246.5</v>
       </c>
       <c r="M12">
-        <v>60.37709300000001</v>
+        <v>66.41480230000001</v>
       </c>
       <c r="N12">
-        <v>186.122907</v>
+        <v>180.0851977</v>
       </c>
       <c r="O12">
-        <v>37.2245814</v>
+        <v>36.01703954</v>
       </c>
       <c r="P12">
-        <v>148.8983256</v>
+        <v>144.06815816</v>
       </c>
       <c r="Q12">
-        <v>785.9983256</v>
+        <v>781.1681581600001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07447578299506843</v>
+        <v>0.07473880324725893</v>
       </c>
       <c r="T12">
-        <v>0.589604280163156</v>
+        <v>0.5950122533818044</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>4.082674202283968</v>
+        <v>3.711522002076335</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07138393489006045</v>
+        <v>0.0713156650845593</v>
       </c>
       <c r="C13">
-        <v>9180.30457972319</v>
+        <v>9098.243486043286</v>
       </c>
       <c r="D13">
-        <v>10135.99557972319</v>
+        <v>10163.11548604329</v>
       </c>
       <c r="E13">
-        <v>-2242.609</v>
+        <v>-2133.428</v>
       </c>
       <c r="F13">
-        <v>1200.991</v>
+        <v>1310.172</v>
       </c>
       <c r="G13">
         <v>245.3</v>
@@ -2359,28 +2359,28 @@
         <v>246.5</v>
       </c>
       <c r="M13">
-        <v>66.41480230000001</v>
+        <v>72.45251160000001</v>
       </c>
       <c r="N13">
-        <v>180.0851977</v>
+        <v>174.0474884</v>
       </c>
       <c r="O13">
-        <v>36.01703954</v>
+        <v>34.80949768</v>
       </c>
       <c r="P13">
-        <v>144.06815816</v>
+        <v>139.23799072</v>
       </c>
       <c r="Q13">
-        <v>781.1681581600001</v>
+        <v>776.33799072</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07473880324725893</v>
+        <v>0.07500780123245375</v>
       </c>
       <c r="T13">
-        <v>0.5950122533818044</v>
+        <v>0.6005431350826951</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.711522002076335</v>
+        <v>3.402228501903307</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0713156650845593</v>
+        <v>0.07124739527905814</v>
       </c>
       <c r="C14">
-        <v>9098.243486043286</v>
+        <v>9016.327905938306</v>
       </c>
       <c r="D14">
-        <v>10163.11548604329</v>
+        <v>10190.38090593831</v>
       </c>
       <c r="E14">
-        <v>-2133.428</v>
+        <v>-2024.247</v>
       </c>
       <c r="F14">
-        <v>1310.172</v>
+        <v>1419.353</v>
       </c>
       <c r="G14">
         <v>245.3</v>
@@ -2441,28 +2441,28 @@
         <v>246.5</v>
       </c>
       <c r="M14">
-        <v>72.45251160000001</v>
+        <v>78.49022090000001</v>
       </c>
       <c r="N14">
-        <v>174.0474884</v>
+        <v>168.0097791</v>
       </c>
       <c r="O14">
-        <v>34.80949768</v>
+        <v>33.60195582</v>
       </c>
       <c r="P14">
-        <v>139.23799072</v>
+        <v>134.40782328</v>
       </c>
       <c r="Q14">
-        <v>776.33799072</v>
+        <v>771.50782328</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07500780123245375</v>
+        <v>0.07528298307937718</v>
       </c>
       <c r="T14">
-        <v>0.6005431350826951</v>
+        <v>0.6062011634893532</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.402228501903307</v>
+        <v>3.140518617141514</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07124739527905814</v>
+        <v>0.071459125473557</v>
       </c>
       <c r="C15">
-        <v>9016.327905938306</v>
+        <v>8823.059420826808</v>
       </c>
       <c r="D15">
-        <v>10190.38090593831</v>
+        <v>10106.29342082681</v>
       </c>
       <c r="E15">
-        <v>-2024.247</v>
+        <v>-1915.066</v>
       </c>
       <c r="F15">
-        <v>1419.353</v>
+        <v>1528.534</v>
       </c>
       <c r="G15">
         <v>245.3</v>
@@ -2523,45 +2523,45 @@
         <v>246.5</v>
       </c>
       <c r="M15">
-        <v>78.49022090000001</v>
+        <v>88.34926520000002</v>
       </c>
       <c r="N15">
-        <v>168.0097791</v>
+        <v>158.1507348</v>
       </c>
       <c r="O15">
-        <v>33.60195582</v>
+        <v>31.63014696</v>
       </c>
       <c r="P15">
-        <v>134.40782328</v>
+        <v>126.52058784</v>
       </c>
       <c r="Q15">
-        <v>771.50782328</v>
+        <v>763.62058784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07528298307937718</v>
+        <v>0.07556456450413605</v>
       </c>
       <c r="T15">
-        <v>0.6062011634893532</v>
+        <v>0.6119907739519801</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.140518617141514</v>
+        <v>2.790062819899943</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.071459125473557</v>
+        <v>0.07141085566805586</v>
       </c>
       <c r="C16">
-        <v>8823.059420826808</v>
+        <v>8732.926156837022</v>
       </c>
       <c r="D16">
-        <v>10106.29342082681</v>
+        <v>10125.34115683702</v>
       </c>
       <c r="E16">
-        <v>-1915.066</v>
+        <v>-1805.885</v>
       </c>
       <c r="F16">
-        <v>1528.534</v>
+        <v>1637.715</v>
       </c>
       <c r="G16">
         <v>245.3</v>
@@ -2605,28 +2605,28 @@
         <v>246.5</v>
       </c>
       <c r="M16">
-        <v>88.34926520000002</v>
+        <v>94.65992700000002</v>
       </c>
       <c r="N16">
-        <v>158.1507348</v>
+        <v>151.840073</v>
       </c>
       <c r="O16">
-        <v>31.63014696</v>
+        <v>30.3680146</v>
       </c>
       <c r="P16">
-        <v>126.52058784</v>
+        <v>121.4720584</v>
       </c>
       <c r="Q16">
-        <v>763.62058784</v>
+        <v>758.5720583999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07556456450413605</v>
+        <v>0.07585277137418336</v>
       </c>
       <c r="T16">
-        <v>0.6119907739519801</v>
+        <v>0.6179166105431394</v>
       </c>
       <c r="U16">
         <v>0.0578</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.790062819899943</v>
+        <v>2.604058631906613</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07141085566805586</v>
+        <v>0.07181058586255472</v>
       </c>
       <c r="C17">
-        <v>8732.926156837022</v>
+        <v>8468.139104309903</v>
       </c>
       <c r="D17">
-        <v>10125.34115683702</v>
+        <v>9969.735104309904</v>
       </c>
       <c r="E17">
-        <v>-1805.885</v>
+        <v>-1696.704</v>
       </c>
       <c r="F17">
-        <v>1637.715</v>
+        <v>1746.896</v>
       </c>
       <c r="G17">
         <v>245.3</v>
@@ -2687,45 +2687,45 @@
         <v>246.5</v>
       </c>
       <c r="M17">
-        <v>94.659927</v>
+        <v>107.0847248</v>
       </c>
       <c r="N17">
-        <v>151.840073</v>
+        <v>139.4152752</v>
       </c>
       <c r="O17">
-        <v>30.36801460000001</v>
+        <v>27.88305504</v>
       </c>
       <c r="P17">
-        <v>121.4720584</v>
+        <v>111.53222016</v>
       </c>
       <c r="Q17">
-        <v>758.5720584000001</v>
+        <v>748.63222016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07585277137418336</v>
+        <v>0.07614784031256513</v>
       </c>
       <c r="T17">
-        <v>0.6179166105431394</v>
+        <v>0.6239835384817073</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.604058631906615</v>
+        <v>2.301915613645019</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07181058586255472</v>
+        <v>0.07217111605705356</v>
       </c>
       <c r="C18">
-        <v>8468.139104309903</v>
+        <v>8222.657823029338</v>
       </c>
       <c r="D18">
-        <v>9969.735104309904</v>
+        <v>9833.43482302934</v>
       </c>
       <c r="E18">
-        <v>-1696.704</v>
+        <v>-1587.523</v>
       </c>
       <c r="F18">
-        <v>1746.896</v>
+        <v>1856.077</v>
       </c>
       <c r="G18">
         <v>245.3</v>
@@ -2769,45 +2769,45 @@
         <v>246.5</v>
       </c>
       <c r="M18">
-        <v>107.0847248</v>
+        <v>118.9745357</v>
       </c>
       <c r="N18">
-        <v>139.4152752</v>
+        <v>127.5254643</v>
       </c>
       <c r="O18">
-        <v>27.88305504</v>
+        <v>25.50509286</v>
       </c>
       <c r="P18">
-        <v>111.53222016</v>
+        <v>102.02037144</v>
       </c>
       <c r="Q18">
-        <v>748.63222016</v>
+        <v>739.12037144</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07614784031256513</v>
+        <v>0.07645001934584766</v>
       </c>
       <c r="T18">
-        <v>0.6239835384817073</v>
+        <v>0.6301966574549395</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.301915613645019</v>
+        <v>2.071871922421799</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07217111605705356</v>
+        <v>0.07385804625155243</v>
       </c>
       <c r="C19">
-        <v>8222.657823029338</v>
+        <v>7522.262525002903</v>
       </c>
       <c r="D19">
-        <v>9833.43482302934</v>
+        <v>9242.220525002904</v>
       </c>
       <c r="E19">
-        <v>-1587.523</v>
+        <v>-1478.342</v>
       </c>
       <c r="F19">
-        <v>1856.077</v>
+        <v>1965.258</v>
       </c>
       <c r="G19">
         <v>245.3</v>
@@ -2851,45 +2851,45 @@
         <v>246.5</v>
       </c>
       <c r="M19">
-        <v>118.9745357</v>
+        <v>148.9665564</v>
       </c>
       <c r="N19">
-        <v>127.5254643</v>
+        <v>97.53344359999997</v>
       </c>
       <c r="O19">
-        <v>25.50509286</v>
+        <v>19.50668872</v>
       </c>
       <c r="P19">
-        <v>102.02037144</v>
+        <v>78.02675487999997</v>
       </c>
       <c r="Q19">
-        <v>739.12037144</v>
+        <v>715.12675488</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07645001934584766</v>
+        <v>0.07675956859945418</v>
       </c>
       <c r="T19">
-        <v>0.6301966574549395</v>
+        <v>0.6365613159153238</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05128000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.071871922421799</v>
+        <v>1.65473382722298</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07385804625155243</v>
+        <v>0.07395377644605129</v>
       </c>
       <c r="C20">
-        <v>7522.262525002903</v>
+        <v>7381.655560882058</v>
       </c>
       <c r="D20">
-        <v>9242.220525002904</v>
+        <v>9210.794560882059</v>
       </c>
       <c r="E20">
-        <v>-1478.342</v>
+        <v>-1369.161</v>
       </c>
       <c r="F20">
-        <v>1965.258</v>
+        <v>2074.439</v>
       </c>
       <c r="G20">
         <v>245.3</v>
@@ -2933,28 +2933,28 @@
         <v>246.5</v>
       </c>
       <c r="M20">
-        <v>148.9665564</v>
+        <v>157.2424762</v>
       </c>
       <c r="N20">
-        <v>97.5334436</v>
+        <v>89.25752379999997</v>
       </c>
       <c r="O20">
-        <v>19.50668872</v>
+        <v>17.85150475999999</v>
       </c>
       <c r="P20">
-        <v>78.02675488</v>
+        <v>71.40601903999998</v>
       </c>
       <c r="Q20">
-        <v>715.12675488</v>
+        <v>708.50601904</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07675956859945417</v>
+        <v>0.07707676104450775</v>
       </c>
       <c r="T20">
-        <v>0.6365613159153236</v>
+        <v>0.6430831264364582</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.654733827222981</v>
+        <v>1.567642573158613</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07395377644605129</v>
+        <v>0.07632150664055012</v>
       </c>
       <c r="C21">
-        <v>7381.655560882058</v>
+        <v>6557.939834468794</v>
       </c>
       <c r="D21">
-        <v>9210.794560882059</v>
+        <v>8496.259834468796</v>
       </c>
       <c r="E21">
-        <v>-1369.161</v>
+        <v>-1259.98</v>
       </c>
       <c r="F21">
-        <v>2074.439</v>
+        <v>2183.62</v>
       </c>
       <c r="G21">
         <v>245.3</v>
@@ -3015,45 +3015,45 @@
         <v>246.5</v>
       </c>
       <c r="M21">
-        <v>157.2424762</v>
+        <v>196.5258</v>
       </c>
       <c r="N21">
-        <v>89.25752379999997</v>
+        <v>49.97419999999997</v>
       </c>
       <c r="O21">
-        <v>17.85150475999999</v>
+        <v>9.994839999999995</v>
       </c>
       <c r="P21">
-        <v>71.40601903999998</v>
+        <v>39.97935999999997</v>
       </c>
       <c r="Q21">
-        <v>708.50601904</v>
+        <v>677.07936</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07707676104450775</v>
+        <v>0.07740188330068766</v>
       </c>
       <c r="T21">
-        <v>0.6430831264364582</v>
+        <v>0.6497679822206208</v>
       </c>
       <c r="U21">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.567642573158613</v>
+        <v>1.254288241035019</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07632150664055012</v>
+        <v>0.08190482080075728</v>
       </c>
       <c r="C22">
-        <v>6557.939834468794</v>
+        <v>5134.881995019312</v>
       </c>
       <c r="D22">
-        <v>8496.259834468796</v>
+        <v>7182.382995019312</v>
       </c>
       <c r="E22">
-        <v>-1259.98</v>
+        <v>-1150.799</v>
       </c>
       <c r="F22">
-        <v>2183.62</v>
+        <v>2292.801</v>
       </c>
       <c r="G22">
         <v>245.3</v>
@@ -3097,45 +3097,45 @@
         <v>246.5</v>
       </c>
       <c r="M22">
-        <v>196.5258</v>
+        <v>271.9261986000001</v>
       </c>
       <c r="N22">
-        <v>49.97419999999997</v>
+        <v>-25.42619860000008</v>
       </c>
       <c r="O22">
-        <v>9.994839999999995</v>
+        <v>-5.085239720000016</v>
       </c>
       <c r="P22">
-        <v>39.97935999999997</v>
+        <v>-20.34095888000006</v>
       </c>
       <c r="Q22">
-        <v>677.07936</v>
+        <v>616.75904112</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07740188330068766</v>
+        <v>0.07786614996010549</v>
       </c>
       <c r="T22">
-        <v>0.6497679822206208</v>
+        <v>0.6593137933873769</v>
       </c>
       <c r="U22">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V22">
-        <v>0.2</v>
+        <v>0.1812991916697209</v>
       </c>
       <c r="W22">
-        <v>0.07199999999999999</v>
+        <v>0.09709791586797112</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.254288241035019</v>
+        <v>0.9064959583486044</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08190482080075727</v>
+        <v>0.08263282080075726</v>
       </c>
       <c r="C23">
-        <v>5134.881995019316</v>
+        <v>4883.741332232193</v>
       </c>
       <c r="D23">
-        <v>7182.382995019316</v>
+        <v>7040.423332232192</v>
       </c>
       <c r="E23">
-        <v>-1150.799</v>
+        <v>-1041.618</v>
       </c>
       <c r="F23">
-        <v>2292.801</v>
+        <v>2401.982</v>
       </c>
       <c r="G23">
         <v>245.3</v>
@@ -3179,37 +3179,37 @@
         <v>246.5</v>
       </c>
       <c r="M23">
-        <v>271.9261986</v>
+        <v>284.8750652</v>
       </c>
       <c r="N23">
-        <v>-25.42619860000002</v>
+        <v>-38.37506519999999</v>
       </c>
       <c r="O23">
-        <v>-5.085239720000004</v>
+        <v>-7.67501304</v>
       </c>
       <c r="P23">
-        <v>-20.34095888000002</v>
+        <v>-30.70005215999999</v>
       </c>
       <c r="Q23">
-        <v>616.75904112</v>
+        <v>606.39994784</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07786614996010549</v>
+        <v>0.0782772544467735</v>
       </c>
       <c r="T23">
-        <v>0.6593137933873769</v>
+        <v>0.6677665343282407</v>
       </c>
       <c r="U23">
         <v>0.1186</v>
       </c>
       <c r="V23">
-        <v>0.1812991916697209</v>
+        <v>0.1730583193210973</v>
       </c>
       <c r="W23">
-        <v>0.0970979158679711</v>
+        <v>0.09807528332851788</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9064959583486046</v>
+        <v>0.8652915966054863</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08263282080075726</v>
+        <v>0.08336082080075728</v>
       </c>
       <c r="C24">
-        <v>4883.741332232193</v>
+        <v>4638.103564872044</v>
       </c>
       <c r="D24">
-        <v>7040.423332232192</v>
+        <v>6903.966564872044</v>
       </c>
       <c r="E24">
-        <v>-1041.618</v>
+        <v>-932.4369999999999</v>
       </c>
       <c r="F24">
-        <v>2401.982</v>
+        <v>2511.163</v>
       </c>
       <c r="G24">
         <v>245.3</v>
@@ -3261,37 +3261,37 @@
         <v>246.5</v>
       </c>
       <c r="M24">
-        <v>284.8750652</v>
+        <v>297.8239318</v>
       </c>
       <c r="N24">
-        <v>-38.37506519999999</v>
+        <v>-51.32393180000003</v>
       </c>
       <c r="O24">
-        <v>-7.67501304</v>
+        <v>-10.26478636000001</v>
       </c>
       <c r="P24">
-        <v>-30.70005215999999</v>
+        <v>-41.05914544000002</v>
       </c>
       <c r="Q24">
-        <v>606.39994784</v>
+        <v>596.04085456</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0782772544467735</v>
+        <v>0.0786990369720563</v>
       </c>
       <c r="T24">
-        <v>0.6677665343282407</v>
+        <v>0.6764388269818544</v>
       </c>
       <c r="U24">
         <v>0.1186</v>
       </c>
       <c r="V24">
-        <v>0.1730583193210973</v>
+        <v>0.1655340445680061</v>
       </c>
       <c r="W24">
-        <v>0.09807528332851788</v>
+        <v>0.0989676623142345</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8652915966054863</v>
+        <v>0.8276702228400303</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08336082080075728</v>
+        <v>0.1042272658206167</v>
       </c>
       <c r="C25">
-        <v>4638.103564872044</v>
+        <v>2063.271695855739</v>
       </c>
       <c r="D25">
-        <v>6903.966564872044</v>
+        <v>4438.315695855739</v>
       </c>
       <c r="E25">
-        <v>-932.4369999999999</v>
+        <v>-823.2559999999994</v>
       </c>
       <c r="F25">
-        <v>2511.163</v>
+        <v>2620.344000000001</v>
       </c>
       <c r="G25">
         <v>245.3</v>
@@ -3343,45 +3343,45 @@
         <v>246.5</v>
       </c>
       <c r="M25">
-        <v>297.8239318</v>
+        <v>526.1650752000002</v>
       </c>
       <c r="N25">
-        <v>-51.32393180000003</v>
+        <v>-279.6650752000002</v>
       </c>
       <c r="O25">
-        <v>-10.26478636000001</v>
+        <v>-55.93301504000004</v>
       </c>
       <c r="P25">
-        <v>-41.05914544000002</v>
+        <v>-223.7320601600001</v>
       </c>
       <c r="Q25">
-        <v>596.04085456</v>
+        <v>413.3679398399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0786990369720563</v>
+        <v>0.07967197827413522</v>
       </c>
       <c r="T25">
-        <v>0.6764388269818544</v>
+        <v>0.6964435241910609</v>
       </c>
       <c r="U25">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1655340445680061</v>
+        <v>0.093696830754608</v>
       </c>
       <c r="W25">
-        <v>0.0989676623142345</v>
+        <v>0.1819856763844747</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8276702228400303</v>
+        <v>0.46848415377304</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1042272658206167</v>
+        <v>0.1057772658206167</v>
       </c>
       <c r="C26">
-        <v>2063.271695855739</v>
+        <v>1839.390746892549</v>
       </c>
       <c r="D26">
-        <v>4438.315695855739</v>
+        <v>4323.615746892549</v>
       </c>
       <c r="E26">
-        <v>-823.2559999999999</v>
+        <v>-714.0749999999998</v>
       </c>
       <c r="F26">
-        <v>2620.344</v>
+        <v>2729.525</v>
       </c>
       <c r="G26">
         <v>245.3</v>
@@ -3425,37 +3425,37 @@
         <v>246.5</v>
       </c>
       <c r="M26">
-        <v>526.1650752</v>
+        <v>548.08862</v>
       </c>
       <c r="N26">
-        <v>-279.6650752</v>
+        <v>-301.58862</v>
       </c>
       <c r="O26">
-        <v>-55.93301504000002</v>
+        <v>-60.317724</v>
       </c>
       <c r="P26">
-        <v>-223.73206016</v>
+        <v>-241.270896</v>
       </c>
       <c r="Q26">
-        <v>413.36793984</v>
+        <v>395.829104</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07967197827413522</v>
+        <v>0.0801236046511237</v>
       </c>
       <c r="T26">
-        <v>0.6964435241910609</v>
+        <v>0.7057294378469418</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.09369683075460801</v>
+        <v>0.08994895752442371</v>
       </c>
       <c r="W26">
-        <v>0.1819856763844747</v>
+        <v>0.1827382493290957</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4684841537730401</v>
+        <v>0.4497447876221184</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1057772658206167</v>
+        <v>0.1073272658206167</v>
       </c>
       <c r="C27">
-        <v>1839.390746892549</v>
+        <v>1621.288859245406</v>
       </c>
       <c r="D27">
-        <v>4323.615746892549</v>
+        <v>4214.694859245405</v>
       </c>
       <c r="E27">
-        <v>-714.0749999999998</v>
+        <v>-604.8939999999998</v>
       </c>
       <c r="F27">
-        <v>2729.525</v>
+        <v>2838.706</v>
       </c>
       <c r="G27">
         <v>245.3</v>
@@ -3507,37 +3507,37 @@
         <v>246.5</v>
       </c>
       <c r="M27">
-        <v>548.08862</v>
+        <v>570.0121648000001</v>
       </c>
       <c r="N27">
-        <v>-301.58862</v>
+        <v>-323.5121648000001</v>
       </c>
       <c r="O27">
-        <v>-60.317724</v>
+        <v>-64.70243296000001</v>
       </c>
       <c r="P27">
-        <v>-241.270896</v>
+        <v>-258.80973184</v>
       </c>
       <c r="Q27">
-        <v>395.829104</v>
+        <v>378.29026816</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0801236046511237</v>
+        <v>0.08058743714640915</v>
       </c>
       <c r="T27">
-        <v>0.7057294378469418</v>
+        <v>0.7152663221421707</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.08994895752442371</v>
+        <v>0.08648938223502278</v>
       </c>
       <c r="W27">
-        <v>0.1827382493290957</v>
+        <v>0.1834329320472074</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4497447876221184</v>
+        <v>0.4324469111751139</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1073272658206167</v>
+        <v>0.1088772658206167</v>
       </c>
       <c r="C28">
-        <v>1621.288859245406</v>
+        <v>1408.540005648058</v>
       </c>
       <c r="D28">
-        <v>4214.694859245405</v>
+        <v>4111.127005648058</v>
       </c>
       <c r="E28">
-        <v>-604.8939999999998</v>
+        <v>-495.7129999999997</v>
       </c>
       <c r="F28">
-        <v>2838.706</v>
+        <v>2947.887</v>
       </c>
       <c r="G28">
         <v>245.3</v>
@@ -3589,37 +3589,37 @@
         <v>246.5</v>
       </c>
       <c r="M28">
-        <v>570.0121648000001</v>
+        <v>591.9357096000001</v>
       </c>
       <c r="N28">
-        <v>-323.5121648000001</v>
+        <v>-345.4357096000001</v>
       </c>
       <c r="O28">
-        <v>-64.70243296000001</v>
+        <v>-69.08714192000002</v>
       </c>
       <c r="P28">
-        <v>-258.80973184</v>
+        <v>-276.3485676800001</v>
       </c>
       <c r="Q28">
-        <v>378.29026816</v>
+        <v>360.7514323199999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08058743714640915</v>
+        <v>0.08106397738129147</v>
       </c>
       <c r="T28">
-        <v>0.7152663221421707</v>
+        <v>0.7250644909386388</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.08648938223502278</v>
+        <v>0.08328607178187379</v>
       </c>
       <c r="W28">
-        <v>0.1834329320472074</v>
+        <v>0.1840761567861998</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4324469111751139</v>
+        <v>0.4164303589093689</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1088772658206167</v>
+        <v>0.1104272658206167</v>
       </c>
       <c r="C29">
-        <v>1408.540005648058</v>
+        <v>1200.759029649667</v>
       </c>
       <c r="D29">
-        <v>4111.127005648058</v>
+        <v>4012.527029649667</v>
       </c>
       <c r="E29">
-        <v>-495.7129999999997</v>
+        <v>-386.5319999999997</v>
       </c>
       <c r="F29">
-        <v>2947.887</v>
+        <v>3057.068</v>
       </c>
       <c r="G29">
         <v>245.3</v>
@@ -3671,37 +3671,37 @@
         <v>246.5</v>
       </c>
       <c r="M29">
-        <v>591.9357096000001</v>
+        <v>613.8592544000001</v>
       </c>
       <c r="N29">
-        <v>-345.4357096000001</v>
+        <v>-367.3592544000001</v>
       </c>
       <c r="O29">
-        <v>-69.08714192000002</v>
+        <v>-73.47185088000002</v>
       </c>
       <c r="P29">
-        <v>-276.3485676800001</v>
+        <v>-293.88740352</v>
       </c>
       <c r="Q29">
-        <v>360.7514323199999</v>
+        <v>343.21259648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08106397738129147</v>
+        <v>0.08155375484492053</v>
       </c>
       <c r="T29">
-        <v>0.7250644909386388</v>
+        <v>0.7351348310905644</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.08328607178187379</v>
+        <v>0.08031156921823544</v>
       </c>
       <c r="W29">
-        <v>0.1840761567861998</v>
+        <v>0.1846734369009783</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4164303589093689</v>
+        <v>0.4015578460911772</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1104272658206167</v>
+        <v>0.1119772658206167</v>
       </c>
       <c r="C30">
-        <v>1200.759029649667</v>
+        <v>997.5968592456848</v>
       </c>
       <c r="D30">
-        <v>4012.527029649667</v>
+        <v>3918.545859245685</v>
       </c>
       <c r="E30">
-        <v>-386.5319999999997</v>
+        <v>-277.3509999999992</v>
       </c>
       <c r="F30">
-        <v>3057.068</v>
+        <v>3166.249000000001</v>
       </c>
       <c r="G30">
         <v>245.3</v>
@@ -3753,37 +3753,37 @@
         <v>246.5</v>
       </c>
       <c r="M30">
-        <v>613.8592544000001</v>
+        <v>635.7827992000001</v>
       </c>
       <c r="N30">
-        <v>-367.3592544000001</v>
+        <v>-389.2827992000001</v>
       </c>
       <c r="O30">
-        <v>-73.47185088000002</v>
+        <v>-77.85655984000003</v>
       </c>
       <c r="P30">
-        <v>-293.88740352</v>
+        <v>-311.4262393600001</v>
       </c>
       <c r="Q30">
-        <v>343.21259648</v>
+        <v>325.67376064</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08155375484492053</v>
+        <v>0.08205732885682081</v>
       </c>
       <c r="T30">
-        <v>0.7351348310905644</v>
+        <v>0.7454888427960652</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.08031156921823544</v>
+        <v>0.07754220476243422</v>
       </c>
       <c r="W30">
-        <v>0.1846734369009783</v>
+        <v>0.1852295252837032</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4015578460911772</v>
+        <v>0.387711023812171</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1119772658206167</v>
+        <v>0.1135272658206167</v>
       </c>
       <c r="C31">
-        <v>997.5968592456857</v>
+        <v>798.7363777512196</v>
       </c>
       <c r="D31">
-        <v>3918.545859245685</v>
+        <v>3828.866377751219</v>
       </c>
       <c r="E31">
-        <v>-277.3510000000001</v>
+        <v>-168.1700000000001</v>
       </c>
       <c r="F31">
-        <v>3166.249</v>
+        <v>3275.43</v>
       </c>
       <c r="G31">
         <v>245.3</v>
@@ -3835,37 +3835,37 @@
         <v>246.5</v>
       </c>
       <c r="M31">
-        <v>635.7827992</v>
+        <v>657.7063439999999</v>
       </c>
       <c r="N31">
-        <v>-389.2827992</v>
+        <v>-411.2063439999999</v>
       </c>
       <c r="O31">
-        <v>-77.85655984</v>
+        <v>-82.2412688</v>
       </c>
       <c r="P31">
-        <v>-311.42623936</v>
+        <v>-328.9650751999999</v>
       </c>
       <c r="Q31">
-        <v>325.67376064</v>
+        <v>308.1349248000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08205732885682081</v>
+        <v>0.08257529069763253</v>
       </c>
       <c r="T31">
-        <v>0.7454888427960652</v>
+        <v>0.7561386834074376</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.07754220476243423</v>
+        <v>0.07495746460368642</v>
       </c>
       <c r="W31">
-        <v>0.1852295252837032</v>
+        <v>0.1857485411075798</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3877110238121712</v>
+        <v>0.3747873230184321</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1135272658206167</v>
+        <v>0.1150772658206167</v>
       </c>
       <c r="C32">
-        <v>798.7363777512196</v>
+        <v>603.8888489814276</v>
       </c>
       <c r="D32">
-        <v>3828.866377751219</v>
+        <v>3743.199848981427</v>
       </c>
       <c r="E32">
-        <v>-168.1700000000001</v>
+        <v>-58.98900000000003</v>
       </c>
       <c r="F32">
-        <v>3275.43</v>
+        <v>3384.611</v>
       </c>
       <c r="G32">
         <v>245.3</v>
@@ -3917,37 +3917,37 @@
         <v>246.5</v>
       </c>
       <c r="M32">
-        <v>657.7063439999999</v>
+        <v>679.6298888</v>
       </c>
       <c r="N32">
-        <v>-411.2063439999999</v>
+        <v>-433.1298888</v>
       </c>
       <c r="O32">
-        <v>-82.2412688</v>
+        <v>-86.62597776000001</v>
       </c>
       <c r="P32">
-        <v>-328.9650751999999</v>
+        <v>-346.50391104</v>
       </c>
       <c r="Q32">
-        <v>308.1349248000001</v>
+        <v>290.59608896</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08257529069763253</v>
+        <v>0.08310826592513446</v>
       </c>
       <c r="T32">
-        <v>0.7561386834074376</v>
+        <v>0.7670972150510237</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.07495746460368642</v>
+        <v>0.07253948187453524</v>
       </c>
       <c r="W32">
-        <v>0.1857485411075798</v>
+        <v>0.1862340720395933</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3747873230184321</v>
+        <v>0.3626974093726761</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1150772658206167</v>
+        <v>0.1166272658206167</v>
       </c>
       <c r="C33">
-        <v>603.8888489814276</v>
+        <v>412.7908118249206</v>
       </c>
       <c r="D33">
-        <v>3743.199848981427</v>
+        <v>3661.282811824921</v>
       </c>
       <c r="E33">
-        <v>-58.98900000000003</v>
+        <v>50.19200000000046</v>
       </c>
       <c r="F33">
-        <v>3384.611</v>
+        <v>3493.792</v>
       </c>
       <c r="G33">
         <v>245.3</v>
@@ -3999,37 +3999,37 @@
         <v>246.5</v>
       </c>
       <c r="M33">
-        <v>679.6298888</v>
+        <v>701.5534336000001</v>
       </c>
       <c r="N33">
-        <v>-433.1298888</v>
+        <v>-455.0534336000001</v>
       </c>
       <c r="O33">
-        <v>-86.62597776000001</v>
+        <v>-91.01068672000002</v>
       </c>
       <c r="P33">
-        <v>-346.50391104</v>
+        <v>-364.04274688</v>
       </c>
       <c r="Q33">
-        <v>290.59608896</v>
+        <v>273.05725312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08310826592513446</v>
+        <v>0.08365691689462174</v>
       </c>
       <c r="T33">
-        <v>0.7670972150510237</v>
+        <v>0.7783780564488328</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.07253948187453524</v>
+        <v>0.07027262306595601</v>
       </c>
       <c r="W33">
-        <v>0.1862340720395933</v>
+        <v>0.186689257288356</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3626974093726761</v>
+        <v>0.35136311532978</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1166272658206167</v>
+        <v>0.1181772658206167</v>
       </c>
       <c r="C34">
-        <v>412.7908118249206</v>
+        <v>225.2013738439432</v>
       </c>
       <c r="D34">
-        <v>3661.282811824921</v>
+        <v>3582.874373843943</v>
       </c>
       <c r="E34">
-        <v>50.19200000000046</v>
+        <v>159.3730000000005</v>
       </c>
       <c r="F34">
-        <v>3493.792</v>
+        <v>3602.973</v>
       </c>
       <c r="G34">
         <v>245.3</v>
@@ -4081,37 +4081,37 @@
         <v>246.5</v>
       </c>
       <c r="M34">
-        <v>701.5534336000001</v>
+        <v>723.4769784000001</v>
       </c>
       <c r="N34">
-        <v>-455.0534336000001</v>
+        <v>-476.9769784000001</v>
       </c>
       <c r="O34">
-        <v>-91.01068672000002</v>
+        <v>-95.39539568000004</v>
       </c>
       <c r="P34">
-        <v>-364.04274688</v>
+        <v>-381.5815827200001</v>
       </c>
       <c r="Q34">
-        <v>273.05725312</v>
+        <v>255.5184172799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08365691689462174</v>
+        <v>0.08422194550498921</v>
       </c>
       <c r="T34">
-        <v>0.7783780564488328</v>
+        <v>0.789995639380905</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.07027262306595601</v>
+        <v>0.06814314963971491</v>
       </c>
       <c r="W34">
-        <v>0.186689257288356</v>
+        <v>0.1871168555523453</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.35136311532978</v>
+        <v>0.3407157481985745</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1181772658206167</v>
+        <v>0.1197272658206167</v>
       </c>
       <c r="C35">
-        <v>225.2013738439432</v>
+        <v>40.89984533780853</v>
       </c>
       <c r="D35">
-        <v>3582.874373843943</v>
+        <v>3507.753845337809</v>
       </c>
       <c r="E35">
-        <v>159.3730000000005</v>
+        <v>268.5540000000005</v>
       </c>
       <c r="F35">
-        <v>3602.973</v>
+        <v>3712.154</v>
       </c>
       <c r="G35">
         <v>245.3</v>
@@ -4163,37 +4163,37 @@
         <v>246.5</v>
       </c>
       <c r="M35">
-        <v>723.4769784000001</v>
+        <v>745.4005232000001</v>
       </c>
       <c r="N35">
-        <v>-476.9769784000001</v>
+        <v>-498.9005232000001</v>
       </c>
       <c r="O35">
-        <v>-95.39539568000004</v>
+        <v>-99.78010464000002</v>
       </c>
       <c r="P35">
-        <v>-381.5815827200001</v>
+        <v>-399.1204185600001</v>
       </c>
       <c r="Q35">
-        <v>255.5184172799999</v>
+        <v>237.9795814399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08422194550498921</v>
+        <v>0.08480409619445875</v>
       </c>
       <c r="T35">
-        <v>0.789995639380905</v>
+        <v>0.8019652702806156</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.06814314963971491</v>
+        <v>0.0661389393561939</v>
       </c>
       <c r="W35">
-        <v>0.1871168555523453</v>
+        <v>0.1875193009772763</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3407157481985745</v>
+        <v>0.3306946967809694</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1197272658206167</v>
+        <v>0.1212772658206167</v>
       </c>
       <c r="C36">
-        <v>40.89984533780853</v>
+        <v>-140.3163350726145</v>
       </c>
       <c r="D36">
-        <v>3507.753845337809</v>
+        <v>3435.718664927386</v>
       </c>
       <c r="E36">
-        <v>268.5540000000005</v>
+        <v>377.7350000000006</v>
       </c>
       <c r="F36">
-        <v>3712.154</v>
+        <v>3821.335</v>
       </c>
       <c r="G36">
         <v>245.3</v>
@@ -4245,37 +4245,37 @@
         <v>246.5</v>
       </c>
       <c r="M36">
-        <v>745.4005232000001</v>
+        <v>767.3240680000001</v>
       </c>
       <c r="N36">
-        <v>-498.9005232000001</v>
+        <v>-520.8240680000001</v>
       </c>
       <c r="O36">
-        <v>-99.78010464000002</v>
+        <v>-104.1648136</v>
       </c>
       <c r="P36">
-        <v>-399.1204185600001</v>
+        <v>-416.6592544000001</v>
       </c>
       <c r="Q36">
-        <v>237.9795814399999</v>
+        <v>220.4407455999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08480409619445875</v>
+        <v>0.08540415921283503</v>
       </c>
       <c r="T36">
-        <v>0.8019652702806156</v>
+        <v>0.8143031975157021</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.0661389393561939</v>
+        <v>0.06424925537458835</v>
       </c>
       <c r="W36">
-        <v>0.1875193009772763</v>
+        <v>0.1878987495207827</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3306946967809694</v>
+        <v>0.3212462768729417</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1212772658206167</v>
+        <v>0.1228272658206167</v>
       </c>
       <c r="C37">
-        <v>-140.3163350726145</v>
+        <v>-318.633424402843</v>
       </c>
       <c r="D37">
-        <v>3435.718664927386</v>
+        <v>3366.582575597157</v>
       </c>
       <c r="E37">
-        <v>377.7350000000006</v>
+        <v>486.9160000000006</v>
       </c>
       <c r="F37">
-        <v>3821.335</v>
+        <v>3930.516000000001</v>
       </c>
       <c r="G37">
         <v>245.3</v>
@@ -4327,37 +4327,37 @@
         <v>246.5</v>
       </c>
       <c r="M37">
-        <v>767.3240680000001</v>
+        <v>789.2476128000002</v>
       </c>
       <c r="N37">
-        <v>-520.8240680000001</v>
+        <v>-542.7476128000002</v>
       </c>
       <c r="O37">
-        <v>-104.1648136</v>
+        <v>-108.54952256</v>
       </c>
       <c r="P37">
-        <v>-416.6592544000001</v>
+        <v>-434.1980902400002</v>
       </c>
       <c r="Q37">
-        <v>220.4407455999999</v>
+        <v>202.9019097599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08540415921283503</v>
+        <v>0.08602297420053559</v>
       </c>
       <c r="T37">
-        <v>0.8143031975157021</v>
+        <v>0.8270266849768849</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.06424925537458835</v>
+        <v>0.06246455383640534</v>
       </c>
       <c r="W37">
-        <v>0.1878987495207827</v>
+        <v>0.1882571175896498</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3212462768729417</v>
+        <v>0.3123227691820266</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1228272658206167</v>
+        <v>0.1243772658206167</v>
       </c>
       <c r="C38">
-        <v>-318.6334244028426</v>
+        <v>-494.2229833884426</v>
       </c>
       <c r="D38">
-        <v>3366.582575597157</v>
+        <v>3300.174016611557</v>
       </c>
       <c r="E38">
-        <v>486.9160000000002</v>
+        <v>596.0970000000002</v>
       </c>
       <c r="F38">
-        <v>3930.516</v>
+        <v>4039.697</v>
       </c>
       <c r="G38">
         <v>245.3</v>
@@ -4409,37 +4409,37 @@
         <v>246.5</v>
       </c>
       <c r="M38">
-        <v>789.2476128000001</v>
+        <v>811.1711576</v>
       </c>
       <c r="N38">
-        <v>-542.7476128000001</v>
+        <v>-564.6711576</v>
       </c>
       <c r="O38">
-        <v>-108.54952256</v>
+        <v>-112.93423152</v>
       </c>
       <c r="P38">
-        <v>-434.1980902400001</v>
+        <v>-451.73692608</v>
       </c>
       <c r="Q38">
-        <v>202.90190976</v>
+        <v>185.36307392</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08602297420053558</v>
+        <v>0.0866614341084806</v>
       </c>
       <c r="T38">
-        <v>0.8270266849768848</v>
+        <v>0.8401540926749307</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.06246455383640534</v>
+        <v>0.06077632265163763</v>
       </c>
       <c r="W38">
-        <v>0.1882571175896498</v>
+        <v>0.1885961144115512</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3123227691820267</v>
+        <v>0.3038816132581882</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1243772658206167</v>
+        <v>0.1259272658206167</v>
       </c>
       <c r="C39">
-        <v>-494.2229833884426</v>
+        <v>-667.2432979258897</v>
       </c>
       <c r="D39">
-        <v>3300.174016611557</v>
+        <v>3236.334702074111</v>
       </c>
       <c r="E39">
-        <v>596.0970000000002</v>
+        <v>705.2780000000007</v>
       </c>
       <c r="F39">
-        <v>4039.697</v>
+        <v>4148.878000000001</v>
       </c>
       <c r="G39">
         <v>245.3</v>
@@ -4491,37 +4491,37 @@
         <v>246.5</v>
       </c>
       <c r="M39">
-        <v>811.1711576</v>
+        <v>833.0947024000002</v>
       </c>
       <c r="N39">
-        <v>-564.6711576</v>
+        <v>-586.5947024000002</v>
       </c>
       <c r="O39">
-        <v>-112.93423152</v>
+        <v>-117.31894048</v>
       </c>
       <c r="P39">
-        <v>-451.73692608</v>
+        <v>-469.2757619200001</v>
       </c>
       <c r="Q39">
-        <v>185.36307392</v>
+        <v>167.8242380799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0866614341084806</v>
+        <v>0.08732048949732706</v>
       </c>
       <c r="T39">
-        <v>0.8401540926749307</v>
+        <v>0.8537049651374296</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.06077632265163763</v>
+        <v>0.05917694573975242</v>
       </c>
       <c r="W39">
-        <v>0.1885961144115512</v>
+        <v>0.1889172692954577</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3038816132581882</v>
+        <v>0.2958847286987621</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1259272658206167</v>
+        <v>0.1274772658206167</v>
       </c>
       <c r="C40">
-        <v>-667.2432979258897</v>
+        <v>-837.8406386642282</v>
       </c>
       <c r="D40">
-        <v>3236.334702074111</v>
+        <v>3174.918361335772</v>
       </c>
       <c r="E40">
-        <v>705.2780000000007</v>
+        <v>814.4590000000003</v>
       </c>
       <c r="F40">
-        <v>4148.878000000001</v>
+        <v>4258.059</v>
       </c>
       <c r="G40">
         <v>245.3</v>
@@ -4573,37 +4573,37 @@
         <v>246.5</v>
       </c>
       <c r="M40">
-        <v>833.0947024000002</v>
+        <v>855.0182472</v>
       </c>
       <c r="N40">
-        <v>-586.5947024000002</v>
+        <v>-608.5182472</v>
       </c>
       <c r="O40">
-        <v>-117.31894048</v>
+        <v>-121.70364944</v>
       </c>
       <c r="P40">
-        <v>-469.2757619200001</v>
+        <v>-486.81459776</v>
       </c>
       <c r="Q40">
-        <v>167.8242380799999</v>
+        <v>150.28540224</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08732048949732706</v>
+        <v>0.08800115325957832</v>
       </c>
       <c r="T40">
-        <v>0.8537049651374296</v>
+        <v>0.8677001285003382</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05917694573975242</v>
+        <v>0.05765958815668185</v>
       </c>
       <c r="W40">
-        <v>0.1889172692954577</v>
+        <v>0.1892219546981383</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2958847286987621</v>
+        <v>0.2882979407834093</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1274772658206167</v>
+        <v>0.1290272658206167</v>
       </c>
       <c r="C41">
-        <v>-837.8406386642282</v>
+        <v>-1006.150379847162</v>
       </c>
       <c r="D41">
-        <v>3174.918361335772</v>
+        <v>3115.789620152838</v>
       </c>
       <c r="E41">
-        <v>814.4590000000003</v>
+        <v>923.6400000000008</v>
       </c>
       <c r="F41">
-        <v>4258.059</v>
+        <v>4367.240000000001</v>
       </c>
       <c r="G41">
         <v>245.3</v>
@@ -4655,37 +4655,37 @@
         <v>246.5</v>
       </c>
       <c r="M41">
-        <v>855.0182472</v>
+        <v>876.9417920000002</v>
       </c>
       <c r="N41">
-        <v>-608.5182472</v>
+        <v>-630.4417920000002</v>
       </c>
       <c r="O41">
-        <v>-121.70364944</v>
+        <v>-126.0883584</v>
       </c>
       <c r="P41">
-        <v>-486.81459776</v>
+        <v>-504.3534336000001</v>
       </c>
       <c r="Q41">
-        <v>150.28540224</v>
+        <v>132.7465663999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08800115325957832</v>
+        <v>0.08870450581390463</v>
       </c>
       <c r="T41">
-        <v>0.8677001285003382</v>
+        <v>0.8821617973086773</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05765958815668185</v>
+        <v>0.0562180984527648</v>
       </c>
       <c r="W41">
-        <v>0.1892219546981383</v>
+        <v>0.1895114058306848</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2882979407834093</v>
+        <v>0.281090492263824</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1290272658206167</v>
+        <v>0.1305772658206167</v>
       </c>
       <c r="C42">
-        <v>-1006.150379847162</v>
+        <v>-1172.297995419026</v>
       </c>
       <c r="D42">
-        <v>3115.789620152838</v>
+        <v>3058.823004580974</v>
       </c>
       <c r="E42">
-        <v>923.6400000000008</v>
+        <v>1032.821</v>
       </c>
       <c r="F42">
-        <v>4367.240000000001</v>
+        <v>4476.421</v>
       </c>
       <c r="G42">
         <v>245.3</v>
@@ -4737,37 +4737,37 @@
         <v>246.5</v>
       </c>
       <c r="M42">
-        <v>876.9417920000002</v>
+        <v>898.8653368000001</v>
       </c>
       <c r="N42">
-        <v>-630.4417920000002</v>
+        <v>-652.3653368000001</v>
       </c>
       <c r="O42">
-        <v>-126.0883584</v>
+        <v>-130.47306736</v>
       </c>
       <c r="P42">
-        <v>-504.3534336000001</v>
+        <v>-521.8922694400001</v>
       </c>
       <c r="Q42">
-        <v>132.7465663999999</v>
+        <v>115.20773056</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08870450581390463</v>
+        <v>0.08943170082769961</v>
       </c>
       <c r="T42">
-        <v>0.8821617973086773</v>
+        <v>0.8971136921783158</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.0562180984527648</v>
+        <v>0.05484692531977053</v>
       </c>
       <c r="W42">
-        <v>0.1895114058306848</v>
+        <v>0.1897867373957901</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.281090492263824</v>
+        <v>0.2742346265988527</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1305772658206167</v>
+        <v>0.1321272658206167</v>
       </c>
       <c r="C43">
-        <v>-1172.297995419026</v>
+        <v>-1336.399947820698</v>
       </c>
       <c r="D43">
-        <v>3058.823004580974</v>
+        <v>3003.902052179302</v>
       </c>
       <c r="E43">
-        <v>1032.821</v>
+        <v>1142.002000000001</v>
       </c>
       <c r="F43">
-        <v>4476.421</v>
+        <v>4585.602000000001</v>
       </c>
       <c r="G43">
         <v>245.3</v>
@@ -4819,37 +4819,37 @@
         <v>246.5</v>
       </c>
       <c r="M43">
-        <v>898.8653368000001</v>
+        <v>920.7888816000002</v>
       </c>
       <c r="N43">
-        <v>-652.3653368000001</v>
+        <v>-674.2888816000002</v>
       </c>
       <c r="O43">
-        <v>-130.47306736</v>
+        <v>-134.8577763200001</v>
       </c>
       <c r="P43">
-        <v>-521.8922694400001</v>
+        <v>-539.4311052800001</v>
       </c>
       <c r="Q43">
-        <v>115.20773056</v>
+        <v>97.66889471999991</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08943170082769961</v>
+        <v>0.09018397153162547</v>
       </c>
       <c r="T43">
-        <v>0.8971136921783158</v>
+        <v>0.9125811696296661</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05484692531977053</v>
+        <v>0.05354104614549028</v>
       </c>
       <c r="W43">
-        <v>0.1897867373957901</v>
+        <v>0.1900489579339856</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2742346265988527</v>
+        <v>0.2677052307274514</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1321272658206167</v>
+        <v>0.1336772658206167</v>
       </c>
       <c r="C44">
-        <v>-1336.399947820698</v>
+        <v>-1498.564482724736</v>
       </c>
       <c r="D44">
-        <v>3003.902052179301</v>
+        <v>2950.918517275265</v>
       </c>
       <c r="E44">
-        <v>1142.002</v>
+        <v>1251.183</v>
       </c>
       <c r="F44">
-        <v>4585.602</v>
+        <v>4694.783</v>
       </c>
       <c r="G44">
         <v>245.3</v>
@@ -4901,37 +4901,37 @@
         <v>246.5</v>
       </c>
       <c r="M44">
-        <v>920.7888816</v>
+        <v>942.7124264000001</v>
       </c>
       <c r="N44">
-        <v>-674.2888816</v>
+        <v>-696.2124264000001</v>
       </c>
       <c r="O44">
-        <v>-134.85777632</v>
+        <v>-139.24248528</v>
       </c>
       <c r="P44">
-        <v>-539.43110528</v>
+        <v>-556.9699411200002</v>
       </c>
       <c r="Q44">
-        <v>97.66889472000003</v>
+        <v>80.13005887999986</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09018397153162547</v>
+        <v>0.09096263769884697</v>
       </c>
       <c r="T44">
-        <v>0.9125811696296661</v>
+        <v>0.9285913655880813</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.0535410461454903</v>
+        <v>0.05229590553745564</v>
       </c>
       <c r="W44">
-        <v>0.1900489579339856</v>
+        <v>0.1902989821680789</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2677052307274514</v>
+        <v>0.2614795276872781</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1336772658206167</v>
+        <v>0.1352272658206167</v>
       </c>
       <c r="C45">
-        <v>-1498.564482724736</v>
+        <v>-1658.892341121944</v>
       </c>
       <c r="D45">
-        <v>2950.918517275265</v>
+        <v>2899.771658878055</v>
       </c>
       <c r="E45">
-        <v>1251.183</v>
+        <v>1360.364</v>
       </c>
       <c r="F45">
-        <v>4694.783</v>
+        <v>4803.964</v>
       </c>
       <c r="G45">
         <v>245.3</v>
@@ -4983,37 +4983,37 @@
         <v>246.5</v>
       </c>
       <c r="M45">
-        <v>942.7124264000001</v>
+        <v>964.6359712</v>
       </c>
       <c r="N45">
-        <v>-696.2124264000001</v>
+        <v>-718.1359712</v>
       </c>
       <c r="O45">
-        <v>-139.24248528</v>
+        <v>-143.62719424</v>
       </c>
       <c r="P45">
-        <v>-556.9699411200002</v>
+        <v>-574.50877696</v>
       </c>
       <c r="Q45">
-        <v>80.13005887999986</v>
+        <v>62.59122304000005</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09096263769884697</v>
+        <v>0.09176911337204066</v>
       </c>
       <c r="T45">
-        <v>0.9285913655880813</v>
+        <v>0.9451733542592969</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05229590553745564</v>
+        <v>0.05110736222978619</v>
       </c>
       <c r="W45">
-        <v>0.1902989821680789</v>
+        <v>0.1905376416642589</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2614795276872781</v>
+        <v>0.255536811148931</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1352272658206167</v>
+        <v>0.1367772658206167</v>
       </c>
       <c r="C46">
-        <v>-1658.892341121944</v>
+        <v>-1817.47739861608</v>
       </c>
       <c r="D46">
-        <v>2899.771658878055</v>
+        <v>2850.36760138392</v>
       </c>
       <c r="E46">
-        <v>1360.364</v>
+        <v>1469.545000000001</v>
       </c>
       <c r="F46">
-        <v>4803.964</v>
+        <v>4913.145</v>
       </c>
       <c r="G46">
         <v>245.3</v>
@@ -5065,37 +5065,37 @@
         <v>246.5</v>
       </c>
       <c r="M46">
-        <v>964.6359712</v>
+        <v>986.5595160000001</v>
       </c>
       <c r="N46">
-        <v>-718.1359712</v>
+        <v>-740.0595160000001</v>
       </c>
       <c r="O46">
-        <v>-143.62719424</v>
+        <v>-148.0119032</v>
       </c>
       <c r="P46">
-        <v>-574.50877696</v>
+        <v>-592.0476128000001</v>
       </c>
       <c r="Q46">
-        <v>62.59122304000005</v>
+        <v>45.05238719999988</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09176911337204066</v>
+        <v>0.0926049154333505</v>
       </c>
       <c r="T46">
-        <v>0.9451733542592969</v>
+        <v>0.9623583243367387</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05110736222978619</v>
+        <v>0.04997164306912427</v>
       </c>
       <c r="W46">
-        <v>0.1905376416642589</v>
+        <v>0.1907656940717199</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.255536811148931</v>
+        <v>0.2498582153456214</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1367772658206167</v>
+        <v>0.1383272658206167</v>
       </c>
       <c r="C47">
-        <v>-1817.47739861608</v>
+        <v>-1974.407240462443</v>
       </c>
       <c r="D47">
-        <v>2850.36760138392</v>
+        <v>2802.618759537557</v>
       </c>
       <c r="E47">
-        <v>1469.545000000001</v>
+        <v>1578.726</v>
       </c>
       <c r="F47">
-        <v>4913.145</v>
+        <v>5022.326</v>
       </c>
       <c r="G47">
         <v>245.3</v>
@@ -5147,37 +5147,37 @@
         <v>246.5</v>
       </c>
       <c r="M47">
-        <v>986.5595160000001</v>
+        <v>1008.4830608</v>
       </c>
       <c r="N47">
-        <v>-740.0595160000001</v>
+        <v>-761.9830608000001</v>
       </c>
       <c r="O47">
-        <v>-148.0119032</v>
+        <v>-152.39661216</v>
       </c>
       <c r="P47">
-        <v>-592.0476128000001</v>
+        <v>-609.5864486400001</v>
       </c>
       <c r="Q47">
-        <v>45.05238719999988</v>
+        <v>27.51355135999995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0926049154333505</v>
+        <v>0.0934716731265607</v>
       </c>
       <c r="T47">
-        <v>0.9623583243367387</v>
+        <v>0.9801797747874192</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.04997164306912427</v>
+        <v>0.04888530300240418</v>
       </c>
       <c r="W47">
-        <v>0.1907656940717199</v>
+        <v>0.1909838311571173</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2498582153456214</v>
+        <v>0.2444265150120208</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1383272658206167</v>
+        <v>0.1398772658206167</v>
       </c>
       <c r="C48">
-        <v>-1974.407240462443</v>
+        <v>-2129.763679761097</v>
       </c>
       <c r="D48">
-        <v>2802.618759537557</v>
+        <v>2756.443320238903</v>
       </c>
       <c r="E48">
-        <v>1578.726</v>
+        <v>1687.907000000001</v>
       </c>
       <c r="F48">
-        <v>5022.326</v>
+        <v>5131.507000000001</v>
       </c>
       <c r="G48">
         <v>245.3</v>
@@ -5229,37 +5229,37 @@
         <v>246.5</v>
       </c>
       <c r="M48">
-        <v>1008.4830608</v>
+        <v>1030.4066056</v>
       </c>
       <c r="N48">
-        <v>-761.9830608000001</v>
+        <v>-783.9066056000001</v>
       </c>
       <c r="O48">
-        <v>-152.39661216</v>
+        <v>-156.78132112</v>
       </c>
       <c r="P48">
-        <v>-609.5864486400001</v>
+        <v>-627.1252844800001</v>
       </c>
       <c r="Q48">
-        <v>27.51355135999995</v>
+        <v>9.974715519999904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0934716731265607</v>
+        <v>0.09437113865725053</v>
       </c>
       <c r="T48">
-        <v>0.9801797747874192</v>
+        <v>0.9986737328022761</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.04888530300240418</v>
+        <v>0.04784519017256579</v>
       </c>
       <c r="W48">
-        <v>0.1909838311571173</v>
+        <v>0.1911926858133488</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2444265150120208</v>
+        <v>0.2392259508628289</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1398772658206167</v>
+        <v>0.1414272658206167</v>
       </c>
       <c r="C49">
-        <v>-2129.763679761097</v>
+        <v>-2283.62322525444</v>
       </c>
       <c r="D49">
-        <v>2756.443320238903</v>
+        <v>2711.764774745561</v>
       </c>
       <c r="E49">
-        <v>1687.907000000001</v>
+        <v>1797.088000000001</v>
       </c>
       <c r="F49">
-        <v>5131.507000000001</v>
+        <v>5240.688000000001</v>
       </c>
       <c r="G49">
         <v>245.3</v>
@@ -5311,37 +5311,37 @@
         <v>246.5</v>
       </c>
       <c r="M49">
-        <v>1030.4066056</v>
+        <v>1052.3301504</v>
       </c>
       <c r="N49">
-        <v>-783.9066056000001</v>
+        <v>-805.8301504000003</v>
       </c>
       <c r="O49">
-        <v>-156.78132112</v>
+        <v>-161.1660300800001</v>
       </c>
       <c r="P49">
-        <v>-627.1252844800001</v>
+        <v>-644.6641203200003</v>
       </c>
       <c r="Q49">
-        <v>9.974715519999904</v>
+        <v>-7.564120320000256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09437113865725053</v>
+        <v>0.0953051990160438</v>
       </c>
       <c r="T49">
-        <v>0.9986737328022761</v>
+        <v>1.017878996894628</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.04784519017256579</v>
+        <v>0.046848415377304</v>
       </c>
       <c r="W49">
-        <v>0.1911926858133488</v>
+        <v>0.1913928381922374</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2392259508628289</v>
+        <v>0.23424207688652</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1414272658206167</v>
+        <v>0.1429772658206167</v>
       </c>
       <c r="C50">
-        <v>-2283.623225254439</v>
+        <v>-2436.057504355895</v>
       </c>
       <c r="D50">
-        <v>2711.764774745561</v>
+        <v>2668.511495644105</v>
       </c>
       <c r="E50">
-        <v>1797.088</v>
+        <v>1906.269</v>
       </c>
       <c r="F50">
-        <v>5240.688</v>
+        <v>5349.869</v>
       </c>
       <c r="G50">
         <v>245.3</v>
@@ -5393,37 +5393,37 @@
         <v>246.5</v>
       </c>
       <c r="M50">
-        <v>1052.3301504</v>
+        <v>1074.2536952</v>
       </c>
       <c r="N50">
-        <v>-805.8301504000001</v>
+        <v>-827.7536952</v>
       </c>
       <c r="O50">
-        <v>-161.16603008</v>
+        <v>-165.55073904</v>
       </c>
       <c r="P50">
-        <v>-644.6641203200001</v>
+        <v>-662.20295616</v>
       </c>
       <c r="Q50">
-        <v>-7.564120320000029</v>
+        <v>-25.10295615999996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0953051990160438</v>
+        <v>0.09627588919282895</v>
       </c>
       <c r="T50">
-        <v>1.017878996894628</v>
+        <v>1.037837408598444</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.046848415377304</v>
+        <v>0.04589232526756312</v>
       </c>
       <c r="W50">
-        <v>0.1913928381922374</v>
+        <v>0.1915848210862733</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.23424207688652</v>
+        <v>0.2294616263378155</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1429772658206167</v>
+        <v>0.1445272658206167</v>
       </c>
       <c r="C51">
-        <v>-2436.057504355895</v>
+        <v>-2587.133646329782</v>
       </c>
       <c r="D51">
-        <v>2668.511495644105</v>
+        <v>2626.616353670218</v>
       </c>
       <c r="E51">
-        <v>1906.269</v>
+        <v>2015.45</v>
       </c>
       <c r="F51">
-        <v>5349.869</v>
+        <v>5459.05</v>
       </c>
       <c r="G51">
         <v>245.3</v>
@@ -5475,37 +5475,37 @@
         <v>246.5</v>
       </c>
       <c r="M51">
-        <v>1074.2536952</v>
+        <v>1096.17724</v>
       </c>
       <c r="N51">
-        <v>-827.7536952</v>
+        <v>-849.67724</v>
       </c>
       <c r="O51">
-        <v>-165.55073904</v>
+        <v>-169.935448</v>
       </c>
       <c r="P51">
-        <v>-662.20295616</v>
+        <v>-679.741792</v>
       </c>
       <c r="Q51">
-        <v>-25.10295615999996</v>
+        <v>-42.64179200000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09627588919282895</v>
+        <v>0.09728540697668556</v>
       </c>
       <c r="T51">
-        <v>1.037837408598444</v>
+        <v>1.058594156770413</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.04589232526756312</v>
+        <v>0.04497447876221185</v>
       </c>
       <c r="W51">
-        <v>0.1915848210862733</v>
+        <v>0.1917691246645479</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2294616263378155</v>
+        <v>0.2248723938110593</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1445272658206167</v>
+        <v>0.1460772658206167</v>
       </c>
       <c r="C52">
-        <v>-2587.133646329782</v>
+        <v>-2736.91462993396</v>
       </c>
       <c r="D52">
-        <v>2626.616353670218</v>
+        <v>2586.01637006604</v>
       </c>
       <c r="E52">
-        <v>2015.45</v>
+        <v>2124.631000000001</v>
       </c>
       <c r="F52">
-        <v>5459.05</v>
+        <v>5568.231000000001</v>
       </c>
       <c r="G52">
         <v>245.3</v>
@@ -5557,37 +5557,37 @@
         <v>246.5</v>
       </c>
       <c r="M52">
-        <v>1096.17724</v>
+        <v>1118.1007848</v>
       </c>
       <c r="N52">
-        <v>-849.67724</v>
+        <v>-871.6007848000002</v>
       </c>
       <c r="O52">
-        <v>-169.935448</v>
+        <v>-174.32015696</v>
       </c>
       <c r="P52">
-        <v>-679.741792</v>
+        <v>-697.2806278400001</v>
       </c>
       <c r="Q52">
-        <v>-42.64179200000001</v>
+        <v>-60.18062784000006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09728540697668556</v>
+        <v>0.09833612956804648</v>
       </c>
       <c r="T52">
-        <v>1.058594156770413</v>
+        <v>1.080198119153482</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.04497447876221185</v>
+        <v>0.04409262623746259</v>
       </c>
       <c r="W52">
-        <v>0.1917691246645479</v>
+        <v>0.1919462006515175</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2248723938110593</v>
+        <v>0.220463131187313</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1460772658206167</v>
+        <v>0.1476272658206167</v>
       </c>
       <c r="C53">
-        <v>-2736.91462993396</v>
+        <v>-2885.459599311902</v>
       </c>
       <c r="D53">
-        <v>2586.01637006604</v>
+        <v>2546.652400688098</v>
       </c>
       <c r="E53">
-        <v>2124.631000000001</v>
+        <v>2233.812</v>
       </c>
       <c r="F53">
-        <v>5568.231000000001</v>
+        <v>5677.412</v>
       </c>
       <c r="G53">
         <v>245.3</v>
@@ -5639,37 +5639,37 @@
         <v>246.5</v>
       </c>
       <c r="M53">
-        <v>1118.1007848</v>
+        <v>1140.0243296</v>
       </c>
       <c r="N53">
-        <v>-871.6007848000002</v>
+        <v>-893.5243296000001</v>
       </c>
       <c r="O53">
-        <v>-174.32015696</v>
+        <v>-178.70486592</v>
       </c>
       <c r="P53">
-        <v>-697.2806278400001</v>
+        <v>-714.8194636800001</v>
       </c>
       <c r="Q53">
-        <v>-60.18062784000006</v>
+        <v>-77.7194636800001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09833612956804648</v>
+        <v>0.09943063226738078</v>
       </c>
       <c r="T53">
-        <v>1.080198119153482</v>
+        <v>1.102702246635846</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.04409262623746259</v>
+        <v>0.04324469111751139</v>
       </c>
       <c r="W53">
-        <v>0.1919462006515175</v>
+        <v>0.1921164660236037</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.220463131187313</v>
+        <v>0.216223455587557</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1476272658206167</v>
+        <v>0.1491772658206167</v>
       </c>
       <c r="C54">
-        <v>-2885.459599311902</v>
+        <v>-3032.824151466552</v>
       </c>
       <c r="D54">
-        <v>2546.652400688098</v>
+        <v>2508.468848533449</v>
       </c>
       <c r="E54">
-        <v>2233.812</v>
+        <v>2342.993000000001</v>
       </c>
       <c r="F54">
-        <v>5677.412</v>
+        <v>5786.593000000001</v>
       </c>
       <c r="G54">
         <v>245.3</v>
@@ -5721,37 +5721,37 @@
         <v>246.5</v>
       </c>
       <c r="M54">
-        <v>1140.0243296</v>
+        <v>1161.9478744</v>
       </c>
       <c r="N54">
-        <v>-893.5243296000001</v>
+        <v>-915.4478744000003</v>
       </c>
       <c r="O54">
-        <v>-178.70486592</v>
+        <v>-183.0895748800001</v>
       </c>
       <c r="P54">
-        <v>-714.8194636800001</v>
+        <v>-732.3582995200002</v>
       </c>
       <c r="Q54">
-        <v>-77.7194636800001</v>
+        <v>-95.25829952000015</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09943063226738078</v>
+        <v>0.1005717095496655</v>
       </c>
       <c r="T54">
-        <v>1.102702246635846</v>
+        <v>1.126163996564269</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.04324469111751139</v>
+        <v>0.04242875354925645</v>
       </c>
       <c r="W54">
-        <v>0.1921164660236037</v>
+        <v>0.1922803062873093</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.216223455587557</v>
+        <v>0.2121437677462823</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1491772658206167</v>
+        <v>0.1507272658206167</v>
       </c>
       <c r="C55">
-        <v>-3032.824151466552</v>
+        <v>-3179.060598254558</v>
       </c>
       <c r="D55">
-        <v>2508.468848533449</v>
+        <v>2471.413401745443</v>
       </c>
       <c r="E55">
-        <v>2342.993000000001</v>
+        <v>2452.174</v>
       </c>
       <c r="F55">
-        <v>5786.593000000001</v>
+        <v>5895.774</v>
       </c>
       <c r="G55">
         <v>245.3</v>
@@ -5803,37 +5803,37 @@
         <v>246.5</v>
       </c>
       <c r="M55">
-        <v>1161.9478744</v>
+        <v>1183.8714192</v>
       </c>
       <c r="N55">
-        <v>-915.4478744000003</v>
+        <v>-937.3714192000002</v>
       </c>
       <c r="O55">
-        <v>-183.0895748800001</v>
+        <v>-187.4742838400001</v>
       </c>
       <c r="P55">
-        <v>-732.3582995200002</v>
+        <v>-749.8971353600002</v>
       </c>
       <c r="Q55">
-        <v>-95.25829952000015</v>
+        <v>-112.7971353600002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1005717095496655</v>
+        <v>0.1017623988877017</v>
       </c>
       <c r="T55">
-        <v>1.126163996564269</v>
+        <v>1.150645822576535</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.04242875354925645</v>
+        <v>0.0416430358909369</v>
       </c>
       <c r="W55">
-        <v>0.1922803062873093</v>
+        <v>0.1924380783930999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2121437677462823</v>
+        <v>0.2082151794546845</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1507272658206167</v>
+        <v>0.1522772658206167</v>
       </c>
       <c r="C56">
-        <v>-3179.060598254558</v>
+        <v>-3324.218205497263</v>
       </c>
       <c r="D56">
-        <v>2471.413401745443</v>
+        <v>2435.436794502738</v>
       </c>
       <c r="E56">
-        <v>2452.174</v>
+        <v>2561.355000000001</v>
       </c>
       <c r="F56">
-        <v>5895.774</v>
+        <v>6004.955000000001</v>
       </c>
       <c r="G56">
         <v>245.3</v>
@@ -5885,37 +5885,37 @@
         <v>246.5</v>
       </c>
       <c r="M56">
-        <v>1183.8714192</v>
+        <v>1205.794964</v>
       </c>
       <c r="N56">
-        <v>-937.3714192000002</v>
+        <v>-959.2949640000002</v>
       </c>
       <c r="O56">
-        <v>-187.4742838400001</v>
+        <v>-191.8589928</v>
       </c>
       <c r="P56">
-        <v>-749.8971353600002</v>
+        <v>-767.4359712000002</v>
       </c>
       <c r="Q56">
-        <v>-112.7971353600002</v>
+        <v>-130.3359712000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1017623988877017</v>
+        <v>0.1030060077518728</v>
       </c>
       <c r="T56">
-        <v>1.150645822576535</v>
+        <v>1.176215729744903</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.0416430358909369</v>
+        <v>0.04088588978382895</v>
       </c>
       <c r="W56">
-        <v>0.1924380783930999</v>
+        <v>0.1925901133314072</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2082151794546845</v>
+        <v>0.2044294489191447</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1522772658206167</v>
+        <v>0.1538272658206167</v>
       </c>
       <c r="C57">
-        <v>-3324.218205497263</v>
+        <v>-3468.343411506769</v>
       </c>
       <c r="D57">
-        <v>2435.436794502738</v>
+        <v>2400.492588493231</v>
       </c>
       <c r="E57">
-        <v>2561.355000000001</v>
+        <v>2670.536000000001</v>
       </c>
       <c r="F57">
-        <v>6004.955000000001</v>
+        <v>6114.136</v>
       </c>
       <c r="G57">
         <v>245.3</v>
@@ -5967,37 +5967,37 @@
         <v>246.5</v>
       </c>
       <c r="M57">
-        <v>1205.794964</v>
+        <v>1227.7185088</v>
       </c>
       <c r="N57">
-        <v>-959.2949640000002</v>
+        <v>-981.2185088000001</v>
       </c>
       <c r="O57">
-        <v>-191.8589928</v>
+        <v>-196.24370176</v>
       </c>
       <c r="P57">
-        <v>-767.4359712000002</v>
+        <v>-784.9748070400001</v>
       </c>
       <c r="Q57">
-        <v>-130.3359712000001</v>
+        <v>-147.8748070400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1030060077518728</v>
+        <v>0.1043061442916881</v>
       </c>
       <c r="T57">
-        <v>1.176215729744903</v>
+        <v>1.202947905420924</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.04088588978382895</v>
+        <v>0.04015578460911772</v>
       </c>
       <c r="W57">
-        <v>0.1925901133314072</v>
+        <v>0.1927367184504892</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2044294489191447</v>
+        <v>0.2007789230455886</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1538272658206167</v>
+        <v>0.1754151664744677</v>
       </c>
       <c r="C58">
-        <v>-3468.343411506769</v>
+        <v>-3977.335613623349</v>
       </c>
       <c r="D58">
-        <v>2400.492588493231</v>
+        <v>2000.681386376652</v>
       </c>
       <c r="E58">
-        <v>2670.536000000001</v>
+        <v>2779.717000000001</v>
       </c>
       <c r="F58">
-        <v>6114.136</v>
+        <v>6223.317000000001</v>
       </c>
       <c r="G58">
         <v>245.3</v>
@@ -6049,45 +6049,45 @@
         <v>246.5</v>
       </c>
       <c r="M58">
-        <v>1227.7185088</v>
+        <v>1467.4581486</v>
       </c>
       <c r="N58">
-        <v>-981.2185088000001</v>
+        <v>-1220.9581486</v>
       </c>
       <c r="O58">
-        <v>-196.24370176</v>
+        <v>-244.19162972</v>
       </c>
       <c r="P58">
-        <v>-784.9748070400001</v>
+        <v>-976.7665188800001</v>
       </c>
       <c r="Q58">
-        <v>-147.8748070400001</v>
+        <v>-339.6665188800001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1043061442916881</v>
+        <v>0.1058711724237064</v>
       </c>
       <c r="T58">
-        <v>1.202947905420924</v>
+        <v>1.235126531035869</v>
       </c>
       <c r="U58">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04015578460911772</v>
+        <v>0.03359550665689084</v>
       </c>
       <c r="W58">
-        <v>0.1927367184504892</v>
+        <v>0.2278781795303051</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.2007789230455886</v>
+        <v>0.1679775332844542</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1754151664744677</v>
+        <v>0.1773151664744677</v>
       </c>
       <c r="C59">
-        <v>-3977.335613623349</v>
+        <v>-4115.420463544366</v>
       </c>
       <c r="D59">
-        <v>2000.681386376652</v>
+        <v>1971.777536455635</v>
       </c>
       <c r="E59">
-        <v>2779.717000000001</v>
+        <v>2888.898000000002</v>
       </c>
       <c r="F59">
-        <v>6223.317000000001</v>
+        <v>6332.498000000001</v>
       </c>
       <c r="G59">
         <v>245.3</v>
@@ -6131,37 +6131,37 @@
         <v>246.5</v>
       </c>
       <c r="M59">
-        <v>1467.4581486</v>
+        <v>1493.2030284</v>
       </c>
       <c r="N59">
-        <v>-1220.9581486</v>
+        <v>-1246.7030284</v>
       </c>
       <c r="O59">
-        <v>-244.19162972</v>
+        <v>-249.3406056800001</v>
       </c>
       <c r="P59">
-        <v>-976.7665188800001</v>
+        <v>-997.3624227200004</v>
       </c>
       <c r="Q59">
-        <v>-339.6665188800001</v>
+        <v>-360.2624227200004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1058711724237064</v>
+        <v>0.1073014384337947</v>
       </c>
       <c r="T59">
-        <v>1.235126531035869</v>
+        <v>1.264534305584342</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03359550665689084</v>
+        <v>0.03301627378349616</v>
       </c>
       <c r="W59">
-        <v>0.2278781795303051</v>
+        <v>0.2280147626418516</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1679775332844542</v>
+        <v>0.1650813689174808</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1773151664744677</v>
+        <v>0.1792151664744677</v>
       </c>
       <c r="C60">
-        <v>-4115.420463544364</v>
+        <v>-4252.682059013867</v>
       </c>
       <c r="D60">
-        <v>1971.777536455635</v>
+        <v>1943.696940986134</v>
       </c>
       <c r="E60">
-        <v>2888.898</v>
+        <v>2998.079</v>
       </c>
       <c r="F60">
-        <v>6332.498</v>
+        <v>6441.679</v>
       </c>
       <c r="G60">
         <v>245.3</v>
@@ -6213,37 +6213,37 @@
         <v>246.5</v>
       </c>
       <c r="M60">
-        <v>1493.2030284</v>
+        <v>1518.9479082</v>
       </c>
       <c r="N60">
-        <v>-1246.7030284</v>
+        <v>-1272.4479082</v>
       </c>
       <c r="O60">
-        <v>-249.34060568</v>
+        <v>-254.48958164</v>
       </c>
       <c r="P60">
-        <v>-997.36242272</v>
+        <v>-1017.95832656</v>
       </c>
       <c r="Q60">
-        <v>-360.26242272</v>
+        <v>-380.85832656</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1073014384337946</v>
+        <v>0.1088014735175457</v>
       </c>
       <c r="T60">
-        <v>1.264534305584342</v>
+        <v>1.295376605720545</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03301627378349616</v>
+        <v>0.03245667592275894</v>
       </c>
       <c r="W60">
-        <v>0.2280147626418516</v>
+        <v>0.2281467158174135</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1650813689174808</v>
+        <v>0.1622833796137947</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1792151664744677</v>
+        <v>0.1811151664744677</v>
       </c>
       <c r="C61">
-        <v>-4252.682059013867</v>
+        <v>-4389.155078704582</v>
       </c>
       <c r="D61">
-        <v>1943.696940986134</v>
+        <v>1916.404921295418</v>
       </c>
       <c r="E61">
-        <v>2998.079</v>
+        <v>3107.26</v>
       </c>
       <c r="F61">
-        <v>6441.679</v>
+        <v>6550.86</v>
       </c>
       <c r="G61">
         <v>245.3</v>
@@ -6295,37 +6295,37 @@
         <v>246.5</v>
       </c>
       <c r="M61">
-        <v>1518.9479082</v>
+        <v>1544.692788</v>
       </c>
       <c r="N61">
-        <v>-1272.4479082</v>
+        <v>-1298.192788</v>
       </c>
       <c r="O61">
-        <v>-254.48958164</v>
+        <v>-259.6385576</v>
       </c>
       <c r="P61">
-        <v>-1017.95832656</v>
+        <v>-1038.5542304</v>
       </c>
       <c r="Q61">
-        <v>-380.85832656</v>
+        <v>-401.4542304</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1088014735175457</v>
+        <v>0.1103765103554844</v>
       </c>
       <c r="T61">
-        <v>1.295376605720545</v>
+        <v>1.327761020863559</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03245667592275894</v>
+        <v>0.03191573132404629</v>
       </c>
       <c r="W61">
-        <v>0.2281467158174135</v>
+        <v>0.2282742705537899</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1622833796137947</v>
+        <v>0.1595786566202314</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1811151664744677</v>
+        <v>0.1830151664744677</v>
       </c>
       <c r="C62">
-        <v>-4389.155078704582</v>
+        <v>-4524.872280525529</v>
       </c>
       <c r="D62">
-        <v>1916.404921295418</v>
+        <v>1889.868719474471</v>
       </c>
       <c r="E62">
-        <v>3107.26</v>
+        <v>3216.441</v>
       </c>
       <c r="F62">
-        <v>6550.86</v>
+        <v>6660.041</v>
       </c>
       <c r="G62">
         <v>245.3</v>
@@ -6377,37 +6377,37 @@
         <v>246.5</v>
       </c>
       <c r="M62">
-        <v>1544.692788</v>
+        <v>1570.4376678</v>
       </c>
       <c r="N62">
-        <v>-1298.192788</v>
+        <v>-1323.9376678</v>
       </c>
       <c r="O62">
-        <v>-259.6385576</v>
+        <v>-264.78753356</v>
       </c>
       <c r="P62">
-        <v>-1038.5542304</v>
+        <v>-1059.15013424</v>
       </c>
       <c r="Q62">
-        <v>-401.4542304</v>
+        <v>-422.0501342400001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1103765103554844</v>
+        <v>0.1120323183133173</v>
       </c>
       <c r="T62">
-        <v>1.327761020863559</v>
+        <v>1.361806175244676</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03191573132404629</v>
+        <v>0.03139252261381602</v>
       </c>
       <c r="W62">
-        <v>0.2282742705537899</v>
+        <v>0.2283976431676622</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1595786566202314</v>
+        <v>0.1569626130690801</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1830151664744677</v>
+        <v>0.1849151664744677</v>
       </c>
       <c r="C63">
-        <v>-4524.872280525529</v>
+        <v>-4659.864632788551</v>
       </c>
       <c r="D63">
-        <v>1889.868719474471</v>
+        <v>1864.057367211449</v>
       </c>
       <c r="E63">
-        <v>3216.441</v>
+        <v>3325.622</v>
       </c>
       <c r="F63">
-        <v>6660.041</v>
+        <v>6769.222</v>
       </c>
       <c r="G63">
         <v>245.3</v>
@@ -6459,37 +6459,37 @@
         <v>246.5</v>
       </c>
       <c r="M63">
-        <v>1570.4376678</v>
+        <v>1596.1825476</v>
       </c>
       <c r="N63">
-        <v>-1323.9376678</v>
+        <v>-1349.6825476</v>
       </c>
       <c r="O63">
-        <v>-264.78753356</v>
+        <v>-269.93650952</v>
       </c>
       <c r="P63">
-        <v>-1059.15013424</v>
+        <v>-1079.74603808</v>
       </c>
       <c r="Q63">
-        <v>-422.0501342400001</v>
+        <v>-442.6460380799998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1120323183133173</v>
+        <v>0.1137752740584046</v>
       </c>
       <c r="T63">
-        <v>1.361806175244676</v>
+        <v>1.397643179856378</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03139252261381602</v>
+        <v>0.03088619160391577</v>
       </c>
       <c r="W63">
-        <v>0.2283976431676622</v>
+        <v>0.2285170360197967</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1569626130690801</v>
+        <v>0.1544309580195788</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1849151664744677</v>
+        <v>0.1868151664744677</v>
       </c>
       <c r="C64">
-        <v>-4659.864632788551</v>
+        <v>-4794.161434771049</v>
       </c>
       <c r="D64">
-        <v>1864.057367211449</v>
+        <v>1838.94156522895</v>
       </c>
       <c r="E64">
-        <v>3325.622</v>
+        <v>3434.803</v>
       </c>
       <c r="F64">
-        <v>6769.222</v>
+        <v>6878.403</v>
       </c>
       <c r="G64">
         <v>245.3</v>
@@ -6541,37 +6541,37 @@
         <v>246.5</v>
       </c>
       <c r="M64">
-        <v>1596.1825476</v>
+        <v>1621.9274274</v>
       </c>
       <c r="N64">
-        <v>-1349.6825476</v>
+        <v>-1375.4274274</v>
       </c>
       <c r="O64">
-        <v>-269.93650952</v>
+        <v>-275.08548548</v>
       </c>
       <c r="P64">
-        <v>-1079.74603808</v>
+        <v>-1100.34194192</v>
       </c>
       <c r="Q64">
-        <v>-442.6460380799998</v>
+        <v>-463.2419419200002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1137752740584046</v>
+        <v>0.1156124436275507</v>
       </c>
       <c r="T64">
-        <v>1.397643179856378</v>
+        <v>1.435417319852496</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03088619160391577</v>
+        <v>0.0303959345943298</v>
       </c>
       <c r="W64">
-        <v>0.2285170360197967</v>
+        <v>0.2286326386226571</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1544309580195788</v>
+        <v>0.151979672971649</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1868151664744677</v>
+        <v>0.1887151664744677</v>
       </c>
       <c r="C65">
-        <v>-4794.161434771049</v>
+        <v>-4927.790427661709</v>
       </c>
       <c r="D65">
-        <v>1838.94156522895</v>
+        <v>1814.493572338292</v>
       </c>
       <c r="E65">
-        <v>3434.803</v>
+        <v>3543.984000000001</v>
       </c>
       <c r="F65">
-        <v>6878.403</v>
+        <v>6987.584000000001</v>
       </c>
       <c r="G65">
         <v>245.3</v>
@@ -6623,37 +6623,37 @@
         <v>246.5</v>
       </c>
       <c r="M65">
-        <v>1621.9274274</v>
+        <v>1647.6723072</v>
       </c>
       <c r="N65">
-        <v>-1375.4274274</v>
+        <v>-1401.1723072</v>
       </c>
       <c r="O65">
-        <v>-275.08548548</v>
+        <v>-280.2344614400001</v>
       </c>
       <c r="P65">
-        <v>-1100.34194192</v>
+        <v>-1120.93784576</v>
       </c>
       <c r="Q65">
-        <v>-463.2419419200002</v>
+        <v>-483.8378457600001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1156124436275507</v>
+        <v>0.1175516781727604</v>
       </c>
       <c r="T65">
-        <v>1.435417319852496</v>
+        <v>1.475290023181732</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0303959345943298</v>
+        <v>0.0299209981162934</v>
       </c>
       <c r="W65">
-        <v>0.2286326386226571</v>
+        <v>0.228744628644178</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.151979672971649</v>
+        <v>0.149604990581467</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1887151664744677</v>
+        <v>0.1906151664744677</v>
       </c>
       <c r="C66">
-        <v>-4927.790427661709</v>
+        <v>-5060.77789677246</v>
       </c>
       <c r="D66">
-        <v>1814.493572338292</v>
+        <v>1790.68710322754</v>
       </c>
       <c r="E66">
-        <v>3543.984000000001</v>
+        <v>3653.165</v>
       </c>
       <c r="F66">
-        <v>6987.584000000001</v>
+        <v>7096.765</v>
       </c>
       <c r="G66">
         <v>245.3</v>
@@ -6705,37 +6705,37 @@
         <v>246.5</v>
       </c>
       <c r="M66">
-        <v>1647.6723072</v>
+        <v>1673.417187</v>
       </c>
       <c r="N66">
-        <v>-1401.1723072</v>
+        <v>-1426.917187</v>
       </c>
       <c r="O66">
-        <v>-280.2344614400001</v>
+        <v>-285.3834374</v>
       </c>
       <c r="P66">
-        <v>-1120.93784576</v>
+        <v>-1141.5337496</v>
       </c>
       <c r="Q66">
-        <v>-483.8378457600001</v>
+        <v>-504.4337496000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1175516781727604</v>
+        <v>0.1196017261205536</v>
       </c>
       <c r="T66">
-        <v>1.475290023181732</v>
+        <v>1.51744116670121</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0299209981162934</v>
+        <v>0.02946067506835042</v>
       </c>
       <c r="W66">
-        <v>0.228744628644178</v>
+        <v>0.228853172818883</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.149604990581467</v>
+        <v>0.1473033753417521</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1906151664744677</v>
+        <v>0.1925151664744677</v>
       </c>
       <c r="C67">
-        <v>-5060.77789677246</v>
+        <v>-5193.148765808422</v>
       </c>
       <c r="D67">
-        <v>1790.68710322754</v>
+        <v>1767.497234191579</v>
       </c>
       <c r="E67">
-        <v>3653.165</v>
+        <v>3762.346000000001</v>
       </c>
       <c r="F67">
-        <v>7096.765</v>
+        <v>7205.946000000001</v>
       </c>
       <c r="G67">
         <v>245.3</v>
@@ -6787,37 +6787,37 @@
         <v>246.5</v>
       </c>
       <c r="M67">
-        <v>1673.417187</v>
+        <v>1699.1620668</v>
       </c>
       <c r="N67">
-        <v>-1426.917187</v>
+        <v>-1452.6620668</v>
       </c>
       <c r="O67">
-        <v>-285.3834374</v>
+        <v>-290.5324133600001</v>
       </c>
       <c r="P67">
-        <v>-1141.5337496</v>
+        <v>-1162.12965344</v>
       </c>
       <c r="Q67">
-        <v>-504.4337496000002</v>
+        <v>-525.0296534400003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1196017261205536</v>
+        <v>0.1217723651240993</v>
       </c>
       <c r="T67">
-        <v>1.51744116670121</v>
+        <v>1.562071789251246</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02946067506835042</v>
+        <v>0.02901430120367844</v>
       </c>
       <c r="W67">
-        <v>0.228853172818883</v>
+        <v>0.2289584277761726</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1473033753417521</v>
+        <v>0.1450715060183922</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1925151664744677</v>
+        <v>0.1944151664744677</v>
       </c>
       <c r="C68">
-        <v>-5193.148765808422</v>
+        <v>-5324.926683906556</v>
       </c>
       <c r="D68">
-        <v>1767.497234191579</v>
+        <v>1744.900316093445</v>
       </c>
       <c r="E68">
-        <v>3762.346000000001</v>
+        <v>3871.527</v>
       </c>
       <c r="F68">
-        <v>7205.946000000001</v>
+        <v>7315.127</v>
       </c>
       <c r="G68">
         <v>245.3</v>
@@ -6869,37 +6869,37 @@
         <v>246.5</v>
       </c>
       <c r="M68">
-        <v>1699.1620668</v>
+        <v>1724.9069466</v>
       </c>
       <c r="N68">
-        <v>-1452.6620668</v>
+        <v>-1478.4069466</v>
       </c>
       <c r="O68">
-        <v>-290.5324133600001</v>
+        <v>-295.6813893200001</v>
       </c>
       <c r="P68">
-        <v>-1162.12965344</v>
+        <v>-1182.72555728</v>
       </c>
       <c r="Q68">
-        <v>-525.0296534400003</v>
+        <v>-545.62555728</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1217723651240993</v>
+        <v>0.1240745580066477</v>
       </c>
       <c r="T68">
-        <v>1.562071789251246</v>
+        <v>1.609407298016435</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02901430120367844</v>
+        <v>0.02858125193198176</v>
       </c>
       <c r="W68">
-        <v>0.2289584277761726</v>
+        <v>0.2290605407944387</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1450715060183922</v>
+        <v>0.1429062596599088</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1944151664744677</v>
+        <v>0.1963151664744677</v>
       </c>
       <c r="C69">
-        <v>-5324.926683906556</v>
+        <v>-5456.134106082023</v>
       </c>
       <c r="D69">
-        <v>1744.900316093445</v>
+        <v>1722.873893917978</v>
       </c>
       <c r="E69">
-        <v>3871.527</v>
+        <v>3980.708000000001</v>
       </c>
       <c r="F69">
-        <v>7315.127</v>
+        <v>7424.308000000001</v>
       </c>
       <c r="G69">
         <v>245.3</v>
@@ -6951,37 +6951,37 @@
         <v>246.5</v>
       </c>
       <c r="M69">
-        <v>1724.9069466</v>
+        <v>1750.6518264</v>
       </c>
       <c r="N69">
-        <v>-1478.4069466</v>
+        <v>-1504.1518264</v>
       </c>
       <c r="O69">
-        <v>-295.6813893200001</v>
+        <v>-300.8303652800001</v>
       </c>
       <c r="P69">
-        <v>-1182.72555728</v>
+        <v>-1203.32146112</v>
       </c>
       <c r="Q69">
-        <v>-545.62555728</v>
+        <v>-566.2214611200003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1240745580066477</v>
+        <v>0.1265206379443555</v>
       </c>
       <c r="T69">
-        <v>1.609407298016435</v>
+        <v>1.659701276079449</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02858125193198176</v>
+        <v>0.02816093940357025</v>
       </c>
       <c r="W69">
-        <v>0.2290605407944387</v>
+        <v>0.2291596504886382</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1429062596599088</v>
+        <v>0.1408046970178513</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1963151664744677</v>
+        <v>0.1982151664744677</v>
       </c>
       <c r="C70">
-        <v>-5456.134106082023</v>
+        <v>-5586.792367657515</v>
       </c>
       <c r="D70">
-        <v>1722.873893917978</v>
+        <v>1701.396632342486</v>
       </c>
       <c r="E70">
-        <v>3980.708000000001</v>
+        <v>4089.889000000001</v>
       </c>
       <c r="F70">
-        <v>7424.308000000001</v>
+        <v>7533.489</v>
       </c>
       <c r="G70">
         <v>245.3</v>
@@ -7033,37 +7033,37 @@
         <v>246.5</v>
       </c>
       <c r="M70">
-        <v>1750.6518264</v>
+        <v>1776.3967062</v>
       </c>
       <c r="N70">
-        <v>-1504.1518264</v>
+        <v>-1529.8967062</v>
       </c>
       <c r="O70">
-        <v>-300.8303652800001</v>
+        <v>-305.9793412400001</v>
       </c>
       <c r="P70">
-        <v>-1203.32146112</v>
+        <v>-1223.91736496</v>
       </c>
       <c r="Q70">
-        <v>-566.2214611200003</v>
+        <v>-586.8173649600002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1265206379443555</v>
+        <v>0.1291245294909476</v>
       </c>
       <c r="T70">
-        <v>1.659701276079449</v>
+        <v>1.713240026920722</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02816093940357025</v>
+        <v>0.02775280984699677</v>
       </c>
       <c r="W70">
-        <v>0.2291596504886382</v>
+        <v>0.2292558874380782</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1408046970178513</v>
+        <v>0.1387640492349839</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1982151664744677</v>
+        <v>0.2001151664744677</v>
       </c>
       <c r="C71">
-        <v>-5586.792367657515</v>
+        <v>-5716.921753194108</v>
       </c>
       <c r="D71">
-        <v>1701.396632342486</v>
+        <v>1680.448246805894</v>
       </c>
       <c r="E71">
-        <v>4089.889000000001</v>
+        <v>4199.070000000002</v>
       </c>
       <c r="F71">
-        <v>7533.489</v>
+        <v>7642.670000000001</v>
       </c>
       <c r="G71">
         <v>245.3</v>
@@ -7115,37 +7115,37 @@
         <v>246.5</v>
       </c>
       <c r="M71">
-        <v>1776.3967062</v>
+        <v>1802.141586</v>
       </c>
       <c r="N71">
-        <v>-1529.8967062</v>
+        <v>-1555.641586</v>
       </c>
       <c r="O71">
-        <v>-305.9793412400001</v>
+        <v>-311.1283172000001</v>
       </c>
       <c r="P71">
-        <v>-1223.91736496</v>
+        <v>-1244.5132688</v>
       </c>
       <c r="Q71">
-        <v>-586.8173649600002</v>
+        <v>-607.4132688000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1291245294909476</v>
+        <v>0.1319020138073125</v>
       </c>
       <c r="T71">
-        <v>1.713240026920722</v>
+        <v>1.770348027818079</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02775280984699677</v>
+        <v>0.02735634113489682</v>
       </c>
       <c r="W71">
-        <v>0.2292558874380782</v>
+        <v>0.2293493747603913</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1387640492349839</v>
+        <v>0.1367817056744841</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2001151664744677</v>
+        <v>0.2020151664744677</v>
       </c>
       <c r="C72">
-        <v>-5716.921753194108</v>
+        <v>-5846.541560391827</v>
       </c>
       <c r="D72">
-        <v>1680.448246805894</v>
+        <v>1660.009439608174</v>
       </c>
       <c r="E72">
-        <v>4199.070000000002</v>
+        <v>4308.251000000002</v>
       </c>
       <c r="F72">
-        <v>7642.670000000001</v>
+        <v>7751.851000000001</v>
       </c>
       <c r="G72">
         <v>245.3</v>
@@ -7197,37 +7197,37 @@
         <v>246.5</v>
       </c>
       <c r="M72">
-        <v>1802.141586</v>
+        <v>1827.8864658</v>
       </c>
       <c r="N72">
-        <v>-1555.641586</v>
+        <v>-1581.3864658</v>
       </c>
       <c r="O72">
-        <v>-311.1283172000001</v>
+        <v>-316.2772931600001</v>
       </c>
       <c r="P72">
-        <v>-1244.5132688</v>
+        <v>-1265.10917264</v>
       </c>
       <c r="Q72">
-        <v>-607.4132688000003</v>
+        <v>-628.0091726400004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1319020138073125</v>
+        <v>0.1348710487661854</v>
       </c>
       <c r="T72">
-        <v>1.770348027818079</v>
+        <v>1.831394511535944</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02735634113489682</v>
+        <v>0.02697104055553207</v>
       </c>
       <c r="W72">
-        <v>0.2293493747603913</v>
+        <v>0.2294402286370055</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1367817056744841</v>
+        <v>0.1348552027776604</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2020151664744677</v>
+        <v>0.2039151664744677</v>
       </c>
       <c r="C73">
-        <v>-5846.541560391826</v>
+        <v>-5975.670159383003</v>
       </c>
       <c r="D73">
-        <v>1660.009439608173</v>
+        <v>1640.061840616997</v>
       </c>
       <c r="E73">
-        <v>4308.251</v>
+        <v>4417.432000000001</v>
       </c>
       <c r="F73">
-        <v>7751.851</v>
+        <v>7861.032</v>
       </c>
       <c r="G73">
         <v>245.3</v>
@@ -7279,37 +7279,37 @@
         <v>246.5</v>
       </c>
       <c r="M73">
-        <v>1827.8864658</v>
+        <v>1853.6313456</v>
       </c>
       <c r="N73">
-        <v>-1581.3864658</v>
+        <v>-1607.1313456</v>
       </c>
       <c r="O73">
-        <v>-316.27729316</v>
+        <v>-321.42626912</v>
       </c>
       <c r="P73">
-        <v>-1265.10917264</v>
+        <v>-1285.70507648</v>
       </c>
       <c r="Q73">
-        <v>-628.00917264</v>
+        <v>-648.6050764800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1348710487661853</v>
+        <v>0.138052157650692</v>
       </c>
       <c r="T73">
-        <v>1.831394511535943</v>
+        <v>1.896801458376512</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02697104055553208</v>
+        <v>0.02659644277003858</v>
       </c>
       <c r="W73">
-        <v>0.2294402286370055</v>
+        <v>0.2295285587948249</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1348552027776604</v>
+        <v>0.1329822138501929</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2039151664744677</v>
+        <v>0.2058151664744677</v>
       </c>
       <c r="C74">
-        <v>-5975.670159383003</v>
+        <v>-6104.325047801382</v>
       </c>
       <c r="D74">
-        <v>1640.061840616997</v>
+        <v>1620.587952198618</v>
       </c>
       <c r="E74">
-        <v>4417.432000000001</v>
+        <v>4526.612999999999</v>
       </c>
       <c r="F74">
-        <v>7861.032</v>
+        <v>7970.213</v>
       </c>
       <c r="G74">
         <v>245.3</v>
@@ -7361,37 +7361,37 @@
         <v>246.5</v>
       </c>
       <c r="M74">
-        <v>1853.6313456</v>
+        <v>1879.3762254</v>
       </c>
       <c r="N74">
-        <v>-1607.1313456</v>
+        <v>-1632.8762254</v>
       </c>
       <c r="O74">
-        <v>-321.42626912</v>
+        <v>-326.5752450800001</v>
       </c>
       <c r="P74">
-        <v>-1285.70507648</v>
+        <v>-1306.30098032</v>
       </c>
       <c r="Q74">
-        <v>-648.6050764800001</v>
+        <v>-669.20098032</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.138052157650692</v>
+        <v>0.1414689042303472</v>
       </c>
       <c r="T74">
-        <v>1.896801458376512</v>
+        <v>1.967053364242309</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02659644277003858</v>
+        <v>0.0262321079375723</v>
       </c>
       <c r="W74">
-        <v>0.2295285587948249</v>
+        <v>0.2296144689483205</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1329822138501929</v>
+        <v>0.1311605396878615</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2058151664744677</v>
+        <v>0.2077151664744677</v>
       </c>
       <c r="C75">
-        <v>-6104.325047801382</v>
+        <v>-6232.522901973984</v>
       </c>
       <c r="D75">
-        <v>1620.587952198618</v>
+        <v>1601.571098026016</v>
       </c>
       <c r="E75">
-        <v>4526.612999999999</v>
+        <v>4635.794</v>
       </c>
       <c r="F75">
-        <v>7970.213</v>
+        <v>8079.394</v>
       </c>
       <c r="G75">
         <v>245.3</v>
@@ -7443,37 +7443,37 @@
         <v>246.5</v>
       </c>
       <c r="M75">
-        <v>1879.3762254</v>
+        <v>1905.1211052</v>
       </c>
       <c r="N75">
-        <v>-1632.8762254</v>
+        <v>-1658.6211052</v>
       </c>
       <c r="O75">
-        <v>-326.5752450800001</v>
+        <v>-331.72422104</v>
       </c>
       <c r="P75">
-        <v>-1306.30098032</v>
+        <v>-1326.89688416</v>
       </c>
       <c r="Q75">
-        <v>-669.20098032</v>
+        <v>-689.7968841600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1414689042303472</v>
+        <v>0.1451484774699759</v>
       </c>
       <c r="T75">
-        <v>1.967053364242309</v>
+        <v>2.042709262867013</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0262321079375723</v>
+        <v>0.02587761999246996</v>
       </c>
       <c r="W75">
-        <v>0.2296144689483205</v>
+        <v>0.2296980572057756</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1311605396878615</v>
+        <v>0.1293880999623498</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2077151664744677</v>
+        <v>0.2096151664744677</v>
       </c>
       <c r="C76">
-        <v>-6232.522901973984</v>
+        <v>-6360.279624550461</v>
       </c>
       <c r="D76">
-        <v>1601.571098026016</v>
+        <v>1582.995375449539</v>
       </c>
       <c r="E76">
-        <v>4635.794</v>
+        <v>4744.975</v>
       </c>
       <c r="F76">
-        <v>8079.394</v>
+        <v>8188.575000000001</v>
       </c>
       <c r="G76">
         <v>245.3</v>
@@ -7525,37 +7525,37 @@
         <v>246.5</v>
       </c>
       <c r="M76">
-        <v>1905.1211052</v>
+        <v>1930.865985</v>
       </c>
       <c r="N76">
-        <v>-1658.6211052</v>
+        <v>-1684.365985</v>
       </c>
       <c r="O76">
-        <v>-331.72422104</v>
+        <v>-336.8731970000001</v>
       </c>
       <c r="P76">
-        <v>-1326.89688416</v>
+        <v>-1347.492788</v>
       </c>
       <c r="Q76">
-        <v>-689.7968841600001</v>
+        <v>-710.392788</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1451484774699759</v>
+        <v>0.149122416568775</v>
       </c>
       <c r="T76">
-        <v>2.042709262867013</v>
+        <v>2.124417633381694</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02587761999246996</v>
+        <v>0.02553258505923704</v>
       </c>
       <c r="W76">
-        <v>0.2296980572057756</v>
+        <v>0.2297794164430319</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1293880999623498</v>
+        <v>0.1276629252961852</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2096151664744677</v>
+        <v>0.2115151664744677</v>
       </c>
       <c r="C77">
-        <v>-6360.279624550461</v>
+        <v>-6487.610388855939</v>
       </c>
       <c r="D77">
-        <v>1582.995375449539</v>
+        <v>1564.845611144062</v>
       </c>
       <c r="E77">
-        <v>4744.975</v>
+        <v>4854.156000000001</v>
       </c>
       <c r="F77">
-        <v>8188.575000000001</v>
+        <v>8297.756000000001</v>
       </c>
       <c r="G77">
         <v>245.3</v>
@@ -7607,37 +7607,37 @@
         <v>246.5</v>
       </c>
       <c r="M77">
-        <v>1930.865985</v>
+        <v>1956.6108648</v>
       </c>
       <c r="N77">
-        <v>-1684.365985</v>
+        <v>-1710.1108648</v>
       </c>
       <c r="O77">
-        <v>-336.8731970000001</v>
+        <v>-342.0221729600001</v>
       </c>
       <c r="P77">
-        <v>-1347.492788</v>
+        <v>-1368.08869184</v>
       </c>
       <c r="Q77">
-        <v>-710.392788</v>
+        <v>-730.9886918400003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.149122416568775</v>
+        <v>0.1534275172591406</v>
       </c>
       <c r="T77">
-        <v>2.124417633381694</v>
+        <v>2.212935034772598</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02553258505923704</v>
+        <v>0.02519662999266813</v>
       </c>
       <c r="W77">
-        <v>0.2297794164430319</v>
+        <v>0.2298586346477288</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1276629252961852</v>
+        <v>0.1259831499633406</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2115151664744677</v>
+        <v>0.2134151664744677</v>
       </c>
       <c r="C78">
-        <v>-6487.610388855939</v>
+        <v>-6614.529680227241</v>
       </c>
       <c r="D78">
-        <v>1564.845611144062</v>
+        <v>1547.107319772759</v>
       </c>
       <c r="E78">
-        <v>4854.156000000001</v>
+        <v>4963.337</v>
       </c>
       <c r="F78">
-        <v>8297.756000000001</v>
+        <v>8406.937</v>
       </c>
       <c r="G78">
         <v>245.3</v>
@@ -7689,37 +7689,37 @@
         <v>246.5</v>
       </c>
       <c r="M78">
-        <v>1956.6108648</v>
+        <v>1982.3557446</v>
       </c>
       <c r="N78">
-        <v>-1710.1108648</v>
+        <v>-1735.8557446</v>
       </c>
       <c r="O78">
-        <v>-342.0221729600001</v>
+        <v>-347.17114892</v>
       </c>
       <c r="P78">
-        <v>-1368.08869184</v>
+        <v>-1388.68459568</v>
       </c>
       <c r="Q78">
-        <v>-730.9886918400003</v>
+        <v>-751.58459568</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1534275172591406</v>
+        <v>0.1581069745312771</v>
       </c>
       <c r="T78">
-        <v>2.212935034772598</v>
+        <v>2.309149601501841</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02519662999266813</v>
+        <v>0.02486940103172439</v>
       </c>
       <c r="W78">
-        <v>0.2298586346477288</v>
+        <v>0.2299357952367194</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1259831499633406</v>
+        <v>0.124347005158622</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2134151664744677</v>
+        <v>0.2153151664744677</v>
       </c>
       <c r="C79">
-        <v>-6614.529680227241</v>
+        <v>-6741.051334569289</v>
       </c>
       <c r="D79">
-        <v>1547.107319772759</v>
+        <v>1529.766665430712</v>
       </c>
       <c r="E79">
-        <v>4963.337</v>
+        <v>5072.518</v>
       </c>
       <c r="F79">
-        <v>8406.937</v>
+        <v>8516.118</v>
       </c>
       <c r="G79">
         <v>245.3</v>
@@ -7771,37 +7771,37 @@
         <v>246.5</v>
       </c>
       <c r="M79">
-        <v>1982.3557446</v>
+        <v>2008.1006244</v>
       </c>
       <c r="N79">
-        <v>-1735.8557446</v>
+        <v>-1761.6006244</v>
       </c>
       <c r="O79">
-        <v>-347.17114892</v>
+        <v>-352.3201248800001</v>
       </c>
       <c r="P79">
-        <v>-1388.68459568</v>
+        <v>-1409.28049952</v>
       </c>
       <c r="Q79">
-        <v>-751.58459568</v>
+        <v>-772.1804995200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1581069745312771</v>
+        <v>0.1632118370099716</v>
       </c>
       <c r="T79">
-        <v>2.309149601501841</v>
+        <v>2.414110947024653</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02486940103172439</v>
+        <v>0.02455056255695869</v>
       </c>
       <c r="W79">
-        <v>0.2299357952367194</v>
+        <v>0.2300109773490692</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.124347005158622</v>
+        <v>0.1227528127847934</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2153151664744677</v>
+        <v>0.2172151664744677</v>
       </c>
       <c r="C80">
-        <v>-6741.051334569289</v>
+        <v>-6867.188574347239</v>
       </c>
       <c r="D80">
-        <v>1529.766665430712</v>
+        <v>1512.810425652762</v>
       </c>
       <c r="E80">
-        <v>5072.518</v>
+        <v>5181.699000000001</v>
       </c>
       <c r="F80">
-        <v>8516.118</v>
+        <v>8625.299000000001</v>
       </c>
       <c r="G80">
         <v>245.3</v>
@@ -7853,37 +7853,37 @@
         <v>246.5</v>
       </c>
       <c r="M80">
-        <v>2008.1006244</v>
+        <v>2033.8455042</v>
       </c>
       <c r="N80">
-        <v>-1761.6006244</v>
+        <v>-1787.3455042</v>
       </c>
       <c r="O80">
-        <v>-352.3201248800001</v>
+        <v>-357.4691008400001</v>
       </c>
       <c r="P80">
-        <v>-1409.28049952</v>
+        <v>-1429.87640336</v>
       </c>
       <c r="Q80">
-        <v>-772.1804995200001</v>
+        <v>-792.7764033600002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1632118370099716</v>
+        <v>0.1688028768675893</v>
       </c>
       <c r="T80">
-        <v>2.414110947024653</v>
+        <v>2.529068611168684</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02455056255695869</v>
+        <v>0.02423979594231364</v>
       </c>
       <c r="W80">
-        <v>0.2300109773490692</v>
+        <v>0.2300842561168024</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1227528127847934</v>
+        <v>0.1211989797115682</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2172151664744677</v>
+        <v>0.2191151664744677</v>
       </c>
       <c r="C81">
-        <v>-6867.188574347239</v>
+        <v>-6992.954042211243</v>
       </c>
       <c r="D81">
-        <v>1512.810425652762</v>
+        <v>1496.225957788758</v>
       </c>
       <c r="E81">
-        <v>5181.699000000001</v>
+        <v>5290.880000000001</v>
       </c>
       <c r="F81">
-        <v>8625.299000000001</v>
+        <v>8734.480000000001</v>
       </c>
       <c r="G81">
         <v>245.3</v>
@@ -7935,37 +7935,37 @@
         <v>246.5</v>
       </c>
       <c r="M81">
-        <v>2033.8455042</v>
+        <v>2059.590384000001</v>
       </c>
       <c r="N81">
-        <v>-1787.3455042</v>
+        <v>-1813.090384000001</v>
       </c>
       <c r="O81">
-        <v>-357.4691008400001</v>
+        <v>-362.6180768000002</v>
       </c>
       <c r="P81">
-        <v>-1429.87640336</v>
+        <v>-1450.4723072</v>
       </c>
       <c r="Q81">
-        <v>-792.7764033600002</v>
+        <v>-813.3723072000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1688028768675893</v>
+        <v>0.1749530207109688</v>
       </c>
       <c r="T81">
-        <v>2.529068611168684</v>
+        <v>2.655522041727118</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02423979594231364</v>
+        <v>0.02393679849303472</v>
       </c>
       <c r="W81">
-        <v>0.2300842561168024</v>
+        <v>0.2301557029153424</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1211989797115682</v>
+        <v>0.1196839924651736</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2191151664744677</v>
+        <v>0.2210151664744677</v>
       </c>
       <c r="C82">
-        <v>-6992.954042211243</v>
+        <v>-7118.359832433455</v>
       </c>
       <c r="D82">
-        <v>1496.225957788758</v>
+        <v>1480.001167566545</v>
       </c>
       <c r="E82">
-        <v>5290.880000000001</v>
+        <v>5400.061</v>
       </c>
       <c r="F82">
-        <v>8734.480000000001</v>
+        <v>8843.661</v>
       </c>
       <c r="G82">
         <v>245.3</v>
@@ -8017,37 +8017,37 @@
         <v>246.5</v>
       </c>
       <c r="M82">
-        <v>2059.590384000001</v>
+        <v>2085.3352638</v>
       </c>
       <c r="N82">
-        <v>-1813.090384000001</v>
+        <v>-1838.8352638</v>
       </c>
       <c r="O82">
-        <v>-362.6180768000002</v>
+        <v>-367.7670527600001</v>
       </c>
       <c r="P82">
-        <v>-1450.4723072</v>
+        <v>-1471.06821104</v>
       </c>
       <c r="Q82">
-        <v>-813.3723072000004</v>
+        <v>-833.96821104</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1749530207109688</v>
+        <v>0.1817505481168092</v>
       </c>
       <c r="T82">
-        <v>2.655522041727118</v>
+        <v>2.795286359712756</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02393679849303472</v>
+        <v>0.02364128246225651</v>
       </c>
       <c r="W82">
-        <v>0.2301557029153424</v>
+        <v>0.2302253855953999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1196839924651736</v>
+        <v>0.1182064123112826</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2210151664744677</v>
+        <v>0.2229151664744677</v>
       </c>
       <c r="C83">
-        <v>-7118.359832433455</v>
+        <v>-7243.417520321627</v>
       </c>
       <c r="D83">
-        <v>1480.001167566545</v>
+        <v>1464.124479678373</v>
       </c>
       <c r="E83">
-        <v>5400.061</v>
+        <v>5509.242</v>
       </c>
       <c r="F83">
-        <v>8843.661</v>
+        <v>8952.842000000001</v>
       </c>
       <c r="G83">
         <v>245.3</v>
@@ -8099,37 +8099,37 @@
         <v>246.5</v>
       </c>
       <c r="M83">
-        <v>2085.3352638</v>
+        <v>2111.0801436</v>
       </c>
       <c r="N83">
-        <v>-1838.8352638</v>
+        <v>-1864.5801436</v>
       </c>
       <c r="O83">
-        <v>-367.7670527600001</v>
+        <v>-372.91602872</v>
       </c>
       <c r="P83">
-        <v>-1471.06821104</v>
+        <v>-1491.66411488</v>
       </c>
       <c r="Q83">
-        <v>-833.96821104</v>
+        <v>-854.5641148800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1817505481168092</v>
+        <v>0.1893033563455209</v>
       </c>
       <c r="T83">
-        <v>2.795286359712756</v>
+        <v>2.950580046363465</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02364128246225651</v>
+        <v>0.02335297413954607</v>
       </c>
       <c r="W83">
-        <v>0.2302253855953999</v>
+        <v>0.230293368697895</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1182064123112826</v>
+        <v>0.1167648706977303</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2229151664744677</v>
+        <v>0.2248151664744677</v>
       </c>
       <c r="C84">
-        <v>-7243.417520321627</v>
+        <v>-7368.138189759556</v>
       </c>
       <c r="D84">
-        <v>1464.124479678373</v>
+        <v>1448.584810240445</v>
       </c>
       <c r="E84">
-        <v>5509.242</v>
+        <v>5618.423000000001</v>
       </c>
       <c r="F84">
-        <v>8952.842000000001</v>
+        <v>9062.023000000001</v>
       </c>
       <c r="G84">
         <v>245.3</v>
@@ -8181,37 +8181,37 @@
         <v>246.5</v>
       </c>
       <c r="M84">
-        <v>2111.0801436</v>
+        <v>2136.8250234</v>
       </c>
       <c r="N84">
-        <v>-1864.5801436</v>
+        <v>-1890.3250234</v>
       </c>
       <c r="O84">
-        <v>-372.91602872</v>
+        <v>-378.0650046800001</v>
       </c>
       <c r="P84">
-        <v>-1491.66411488</v>
+        <v>-1512.26001872</v>
       </c>
       <c r="Q84">
-        <v>-854.5641148800001</v>
+        <v>-875.16001872</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1893033563455209</v>
+        <v>0.1977447302481986</v>
       </c>
       <c r="T84">
-        <v>2.950580046363465</v>
+        <v>3.124143578502493</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02335297413954607</v>
+        <v>0.02307161300533467</v>
       </c>
       <c r="W84">
-        <v>0.230293368697895</v>
+        <v>0.2303597136533421</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1167648706977303</v>
+        <v>0.1153580650266733</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2248151664744677</v>
+        <v>0.2267151664744677</v>
       </c>
       <c r="C85">
-        <v>-7368.138189759556</v>
+        <v>-7492.532459012167</v>
       </c>
       <c r="D85">
-        <v>1448.584810240445</v>
+        <v>1433.371540987835</v>
       </c>
       <c r="E85">
-        <v>5618.423000000001</v>
+        <v>5727.604000000001</v>
       </c>
       <c r="F85">
-        <v>9062.023000000001</v>
+        <v>9171.204000000002</v>
       </c>
       <c r="G85">
         <v>245.3</v>
@@ -8263,37 +8263,37 @@
         <v>246.5</v>
       </c>
       <c r="M85">
-        <v>2136.8250234</v>
+        <v>2162.5699032</v>
       </c>
       <c r="N85">
-        <v>-1890.3250234</v>
+        <v>-1916.0699032</v>
       </c>
       <c r="O85">
-        <v>-378.0650046800001</v>
+        <v>-383.21398064</v>
       </c>
       <c r="P85">
-        <v>-1512.26001872</v>
+        <v>-1532.85592256</v>
       </c>
       <c r="Q85">
-        <v>-875.16001872</v>
+        <v>-895.7559225600002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1977447302481986</v>
+        <v>0.207241275888711</v>
       </c>
       <c r="T85">
-        <v>3.124143578502493</v>
+        <v>3.319402552158899</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02307161300533467</v>
+        <v>0.02279695094574735</v>
       </c>
       <c r="W85">
-        <v>0.2303597136533421</v>
+        <v>0.2304244789669928</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1153580650266733</v>
+        <v>0.1139847547287367</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2267151664744677</v>
+        <v>0.2286151664744677</v>
       </c>
       <c r="C86">
-        <v>-7492.532459012165</v>
+        <v>-7616.610504921411</v>
       </c>
       <c r="D86">
-        <v>1433.371540987835</v>
+        <v>1418.474495078589</v>
       </c>
       <c r="E86">
-        <v>5727.603999999999</v>
+        <v>5836.785</v>
       </c>
       <c r="F86">
-        <v>9171.204</v>
+        <v>9280.385</v>
       </c>
       <c r="G86">
         <v>245.3</v>
@@ -8345,37 +8345,37 @@
         <v>246.5</v>
       </c>
       <c r="M86">
-        <v>2162.5699032</v>
+        <v>2188.314783</v>
       </c>
       <c r="N86">
-        <v>-1916.0699032</v>
+        <v>-1941.814783</v>
       </c>
       <c r="O86">
-        <v>-383.21398064</v>
+        <v>-388.3629566000001</v>
       </c>
       <c r="P86">
-        <v>-1532.85592256</v>
+        <v>-1553.4518264</v>
       </c>
       <c r="Q86">
-        <v>-895.7559225600002</v>
+        <v>-916.3518264000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2072412758887109</v>
+        <v>0.218004027614625</v>
       </c>
       <c r="T86">
-        <v>3.319402552158897</v>
+        <v>3.540696055636157</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02279695094574735</v>
+        <v>0.02252875152285621</v>
       </c>
       <c r="W86">
-        <v>0.2304244789669928</v>
+        <v>0.2304877203909105</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1139847547287367</v>
+        <v>0.112643757614281</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2286151664744677</v>
+        <v>0.2305151664744677</v>
       </c>
       <c r="C87">
-        <v>-7616.610504921411</v>
+        <v>-7740.382085608906</v>
       </c>
       <c r="D87">
-        <v>1418.474495078589</v>
+        <v>1403.883914391095</v>
       </c>
       <c r="E87">
-        <v>5836.785</v>
+        <v>5945.966</v>
       </c>
       <c r="F87">
-        <v>9280.385</v>
+        <v>9389.566000000001</v>
       </c>
       <c r="G87">
         <v>245.3</v>
@@ -8427,37 +8427,37 @@
         <v>246.5</v>
       </c>
       <c r="M87">
-        <v>2188.314783</v>
+        <v>2214.0596628</v>
       </c>
       <c r="N87">
-        <v>-1941.814783</v>
+        <v>-1967.5596628</v>
       </c>
       <c r="O87">
-        <v>-388.3629566000001</v>
+        <v>-393.5119325600001</v>
       </c>
       <c r="P87">
-        <v>-1553.4518264</v>
+        <v>-1574.04773024</v>
       </c>
       <c r="Q87">
-        <v>-916.3518264000003</v>
+        <v>-936.9477302400002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.218004027614625</v>
+        <v>0.2303043153013839</v>
       </c>
       <c r="T87">
-        <v>3.540696055636157</v>
+        <v>3.793602916753025</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02252875152285621</v>
+        <v>0.02226678929584625</v>
       </c>
       <c r="W87">
-        <v>0.2304877203909105</v>
+        <v>0.2305494910840395</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.112643757614281</v>
+        <v>0.1113339464792312</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2305151664744677</v>
+        <v>0.2324151664744677</v>
       </c>
       <c r="C88">
-        <v>-7740.382085608906</v>
+        <v>-7863.856561791657</v>
       </c>
       <c r="D88">
-        <v>1403.883914391095</v>
+        <v>1389.590438208343</v>
       </c>
       <c r="E88">
-        <v>5945.966</v>
+        <v>6055.146999999999</v>
       </c>
       <c r="F88">
-        <v>9389.566000000001</v>
+        <v>9498.746999999999</v>
       </c>
       <c r="G88">
         <v>245.3</v>
@@ -8509,37 +8509,37 @@
         <v>246.5</v>
       </c>
       <c r="M88">
-        <v>2214.0596628</v>
+        <v>2239.8045426</v>
       </c>
       <c r="N88">
-        <v>-1967.5596628</v>
+        <v>-1993.3045426</v>
       </c>
       <c r="O88">
-        <v>-393.5119325600001</v>
+        <v>-398.66090852</v>
       </c>
       <c r="P88">
-        <v>-1574.04773024</v>
+        <v>-1594.64363408</v>
       </c>
       <c r="Q88">
-        <v>-936.9477302400002</v>
+        <v>-957.5436340799998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2303043153013839</v>
+        <v>0.2444969549399519</v>
       </c>
       <c r="T88">
-        <v>3.793602916753025</v>
+        <v>4.085418525734027</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02226678929584625</v>
+        <v>0.02201084918899745</v>
       </c>
       <c r="W88">
-        <v>0.2305494910840395</v>
+        <v>0.2306098417612344</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1113339464792312</v>
+        <v>0.1100542459449873</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2324151664744677</v>
+        <v>0.2343151664744677</v>
       </c>
       <c r="C89">
-        <v>-7863.856561791657</v>
+        <v>-7987.042916808826</v>
       </c>
       <c r="D89">
-        <v>1389.590438208343</v>
+        <v>1375.585083191174</v>
       </c>
       <c r="E89">
-        <v>6055.146999999999</v>
+        <v>6164.328</v>
       </c>
       <c r="F89">
-        <v>9498.746999999999</v>
+        <v>9607.928</v>
       </c>
       <c r="G89">
         <v>245.3</v>
@@ -8591,37 +8591,37 @@
         <v>246.5</v>
       </c>
       <c r="M89">
-        <v>2239.8045426</v>
+        <v>2265.5494224</v>
       </c>
       <c r="N89">
-        <v>-1993.3045426</v>
+        <v>-2019.0494224</v>
       </c>
       <c r="O89">
-        <v>-398.66090852</v>
+        <v>-403.80988448</v>
       </c>
       <c r="P89">
-        <v>-1594.64363408</v>
+        <v>-1615.23953792</v>
       </c>
       <c r="Q89">
-        <v>-957.5436340799998</v>
+        <v>-978.13953792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2444969549399519</v>
+        <v>0.2610550345182812</v>
       </c>
       <c r="T89">
-        <v>4.085418525734027</v>
+        <v>4.425870069545196</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02201084918899745</v>
+        <v>0.02176072590275884</v>
       </c>
       <c r="W89">
-        <v>0.2306098417612344</v>
+        <v>0.2306688208321295</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1100542459449873</v>
+        <v>0.1088036295137942</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2343151664744677</v>
+        <v>0.2362151664744677</v>
       </c>
       <c r="C90">
-        <v>-7987.042916808826</v>
+        <v>-8109.94977544947</v>
       </c>
       <c r="D90">
-        <v>1375.585083191174</v>
+        <v>1361.859224550531</v>
       </c>
       <c r="E90">
-        <v>6164.328</v>
+        <v>6273.509</v>
       </c>
       <c r="F90">
-        <v>9607.928</v>
+        <v>9717.109</v>
       </c>
       <c r="G90">
         <v>245.3</v>
@@ -8673,37 +8673,37 @@
         <v>246.5</v>
       </c>
       <c r="M90">
-        <v>2265.5494224</v>
+        <v>2291.2943022</v>
       </c>
       <c r="N90">
-        <v>-2019.0494224</v>
+        <v>-2044.7943022</v>
       </c>
       <c r="O90">
-        <v>-403.80988448</v>
+        <v>-408.9588604400001</v>
       </c>
       <c r="P90">
-        <v>-1615.23953792</v>
+        <v>-1635.83544176</v>
       </c>
       <c r="Q90">
-        <v>-978.13953792</v>
+        <v>-998.7354417600003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2610550345182812</v>
+        <v>0.2806236740199431</v>
       </c>
       <c r="T90">
-        <v>4.425870069545196</v>
+        <v>4.828221894049305</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02176072590275884</v>
+        <v>0.02151622336452559</v>
       </c>
       <c r="W90">
-        <v>0.2306688208321295</v>
+        <v>0.2307264745306449</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1088036295137942</v>
+        <v>0.1075811168226279</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2362151664744677</v>
+        <v>0.2381151664744677</v>
       </c>
       <c r="C91">
-        <v>-8109.94977544947</v>
+        <v>-8232.585421664229</v>
       </c>
       <c r="D91">
-        <v>1361.859224550531</v>
+        <v>1348.404578335772</v>
       </c>
       <c r="E91">
-        <v>6273.509</v>
+        <v>6382.690000000001</v>
       </c>
       <c r="F91">
-        <v>9717.109</v>
+        <v>9826.290000000001</v>
       </c>
       <c r="G91">
         <v>245.3</v>
@@ -8755,37 +8755,37 @@
         <v>246.5</v>
       </c>
       <c r="M91">
-        <v>2291.2943022</v>
+        <v>2317.039182</v>
       </c>
       <c r="N91">
-        <v>-2044.7943022</v>
+        <v>-2070.539182</v>
       </c>
       <c r="O91">
-        <v>-408.9588604400001</v>
+        <v>-414.1078364000001</v>
       </c>
       <c r="P91">
-        <v>-1635.83544176</v>
+        <v>-1656.4313456</v>
       </c>
       <c r="Q91">
-        <v>-998.7354417600003</v>
+        <v>-1019.3313456</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2806236740199431</v>
+        <v>0.3041060414219375</v>
       </c>
       <c r="T91">
-        <v>4.828221894049305</v>
+        <v>5.311044083454236</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02151622336452559</v>
+        <v>0.02127715421603086</v>
       </c>
       <c r="W91">
-        <v>0.2307264745306449</v>
+        <v>0.2307828470358599</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1075811168226279</v>
+        <v>0.1063857710801543</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2381151664744677</v>
+        <v>0.2400151664744677</v>
       </c>
       <c r="C92">
-        <v>-8232.585421664229</v>
+        <v>-8354.957815237371</v>
       </c>
       <c r="D92">
-        <v>1348.404578335772</v>
+        <v>1335.21318476263</v>
       </c>
       <c r="E92">
-        <v>6382.690000000001</v>
+        <v>6491.871000000001</v>
       </c>
       <c r="F92">
-        <v>9826.290000000001</v>
+        <v>9935.471000000001</v>
       </c>
       <c r="G92">
         <v>245.3</v>
@@ -8837,37 +8837,37 @@
         <v>246.5</v>
       </c>
       <c r="M92">
-        <v>2317.039182</v>
+        <v>2342.7840618</v>
       </c>
       <c r="N92">
-        <v>-2070.539182</v>
+        <v>-2096.2840618</v>
       </c>
       <c r="O92">
-        <v>-414.1078364000001</v>
+        <v>-419.2568123600001</v>
       </c>
       <c r="P92">
-        <v>-1656.4313456</v>
+        <v>-1677.02724944</v>
       </c>
       <c r="Q92">
-        <v>-1019.3313456</v>
+        <v>-1039.92724944</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3041060414219375</v>
+        <v>0.3328067126910417</v>
       </c>
       <c r="T92">
-        <v>5.311044083454236</v>
+        <v>5.901160092726929</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02127715421603086</v>
+        <v>0.02104333933453601</v>
       </c>
       <c r="W92">
-        <v>0.2307828470358599</v>
+        <v>0.2308379805849164</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1063857710801543</v>
+        <v>0.1052166966726801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2400151664744677</v>
+        <v>0.2419151664744677</v>
       </c>
       <c r="C93">
-        <v>-8354.957815237371</v>
+        <v>-8477.074607489722</v>
       </c>
       <c r="D93">
-        <v>1335.21318476263</v>
+        <v>1322.277392510279</v>
       </c>
       <c r="E93">
-        <v>6491.871000000001</v>
+        <v>6601.052</v>
       </c>
       <c r="F93">
-        <v>9935.471000000001</v>
+        <v>10044.652</v>
       </c>
       <c r="G93">
         <v>245.3</v>
@@ -8919,37 +8919,37 @@
         <v>246.5</v>
       </c>
       <c r="M93">
-        <v>2342.7840618</v>
+        <v>2368.5289416</v>
       </c>
       <c r="N93">
-        <v>-2096.2840618</v>
+        <v>-2122.0289416</v>
       </c>
       <c r="O93">
-        <v>-419.2568123600001</v>
+        <v>-424.4057883200001</v>
       </c>
       <c r="P93">
-        <v>-1677.02724944</v>
+        <v>-1697.62315328</v>
       </c>
       <c r="Q93">
-        <v>-1039.92724944</v>
+        <v>-1060.52315328</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3328067126910417</v>
+        <v>0.368682551777422</v>
       </c>
       <c r="T93">
-        <v>5.901160092726929</v>
+        <v>6.638805104317798</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02104333933453601</v>
+        <v>0.02081460738524758</v>
       </c>
       <c r="W93">
-        <v>0.2308379805849164</v>
+        <v>0.2308919155785586</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1052166966726801</v>
+        <v>0.1040730369262379</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2419151664744677</v>
+        <v>0.2438151664744677</v>
       </c>
       <c r="C94">
-        <v>-8477.074607489722</v>
+        <v>-8598.943156077537</v>
       </c>
       <c r="D94">
-        <v>1322.277392510279</v>
+        <v>1309.589843922464</v>
       </c>
       <c r="E94">
-        <v>6601.052</v>
+        <v>6710.233</v>
       </c>
       <c r="F94">
-        <v>10044.652</v>
+        <v>10153.833</v>
       </c>
       <c r="G94">
         <v>245.3</v>
@@ -9001,37 +9001,37 @@
         <v>246.5</v>
       </c>
       <c r="M94">
-        <v>2368.5289416</v>
+        <v>2394.2738214</v>
       </c>
       <c r="N94">
-        <v>-2122.0289416</v>
+        <v>-2147.7738214</v>
       </c>
       <c r="O94">
-        <v>-424.4057883200001</v>
+        <v>-429.55476428</v>
       </c>
       <c r="P94">
-        <v>-1697.62315328</v>
+        <v>-1718.21905712</v>
       </c>
       <c r="Q94">
-        <v>-1060.52315328</v>
+        <v>-1081.11905712</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.368682551777422</v>
+        <v>0.4148086306027681</v>
       </c>
       <c r="T94">
-        <v>6.638805104317798</v>
+        <v>7.587205833506056</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02081460738524758</v>
+        <v>0.02059079440261051</v>
       </c>
       <c r="W94">
-        <v>0.2308919155785586</v>
+        <v>0.2309446906798645</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1040730369262379</v>
+        <v>0.1029539720130526</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2438151664744677</v>
+        <v>0.2457151664744677</v>
       </c>
       <c r="C95">
-        <v>-8598.943156077537</v>
+        <v>-8720.570538947497</v>
       </c>
       <c r="D95">
-        <v>1309.589843922464</v>
+        <v>1297.143461052505</v>
       </c>
       <c r="E95">
-        <v>6710.233</v>
+        <v>6819.414000000001</v>
       </c>
       <c r="F95">
-        <v>10153.833</v>
+        <v>10263.014</v>
       </c>
       <c r="G95">
         <v>245.3</v>
@@ -9083,37 +9083,37 @@
         <v>246.5</v>
       </c>
       <c r="M95">
-        <v>2394.2738214</v>
+        <v>2420.0187012</v>
       </c>
       <c r="N95">
-        <v>-2147.7738214</v>
+        <v>-2173.5187012</v>
       </c>
       <c r="O95">
-        <v>-429.55476428</v>
+        <v>-434.7037402400001</v>
       </c>
       <c r="P95">
-        <v>-1718.21905712</v>
+        <v>-1738.81496096</v>
       </c>
       <c r="Q95">
-        <v>-1081.11905712</v>
+        <v>-1101.71496096</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4148086306027681</v>
+        <v>0.4763100690365629</v>
       </c>
       <c r="T95">
-        <v>7.587205833506056</v>
+        <v>8.851740139090401</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02059079440261051</v>
+        <v>0.02037174339832742</v>
       </c>
       <c r="W95">
-        <v>0.2309446906798645</v>
+        <v>0.2309963429066744</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1029539720130526</v>
+        <v>0.1018587169916371</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2457151664744677</v>
+        <v>0.2476151664744677</v>
       </c>
       <c r="C96">
-        <v>-8720.570538947497</v>
+        <v>-8841.963567503395</v>
       </c>
       <c r="D96">
-        <v>1297.143461052505</v>
+        <v>1284.931432496606</v>
       </c>
       <c r="E96">
-        <v>6819.414000000001</v>
+        <v>6928.595000000001</v>
       </c>
       <c r="F96">
-        <v>10263.014</v>
+        <v>10372.195</v>
       </c>
       <c r="G96">
         <v>245.3</v>
@@ -9165,37 +9165,37 @@
         <v>246.5</v>
       </c>
       <c r="M96">
-        <v>2420.0187012</v>
+        <v>2445.763581000001</v>
       </c>
       <c r="N96">
-        <v>-2173.5187012</v>
+        <v>-2199.263581000001</v>
       </c>
       <c r="O96">
-        <v>-434.7037402400001</v>
+        <v>-439.8527162000001</v>
       </c>
       <c r="P96">
-        <v>-1738.81496096</v>
+        <v>-1759.410864800001</v>
       </c>
       <c r="Q96">
-        <v>-1101.71496096</v>
+        <v>-1122.310864800001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4763100690365629</v>
+        <v>0.5624120828438756</v>
       </c>
       <c r="T96">
-        <v>8.851740139090401</v>
+        <v>10.62208816690849</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02037174339832742</v>
+        <v>0.0201573039941345</v>
       </c>
       <c r="W96">
-        <v>0.2309963429066744</v>
+        <v>0.2310469077181831</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1018587169916371</v>
+        <v>0.1007865199706725</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2476151664744677</v>
+        <v>0.2495151664744677</v>
       </c>
       <c r="C97">
-        <v>-8841.963567503395</v>
+        <v>-8963.128799036052</v>
       </c>
       <c r="D97">
-        <v>1284.931432496606</v>
+        <v>1272.94720096395</v>
       </c>
       <c r="E97">
-        <v>6928.595000000001</v>
+        <v>7037.776000000002</v>
       </c>
       <c r="F97">
-        <v>10372.195</v>
+        <v>10481.376</v>
       </c>
       <c r="G97">
         <v>245.3</v>
@@ -9247,37 +9247,37 @@
         <v>246.5</v>
       </c>
       <c r="M97">
-        <v>2445.763581000001</v>
+        <v>2471.508460800001</v>
       </c>
       <c r="N97">
-        <v>-2199.263581000001</v>
+        <v>-2225.008460800001</v>
       </c>
       <c r="O97">
-        <v>-439.8527162000001</v>
+        <v>-445.0016921600002</v>
       </c>
       <c r="P97">
-        <v>-1759.410864800001</v>
+        <v>-1780.00676864</v>
       </c>
       <c r="Q97">
-        <v>-1122.310864800001</v>
+        <v>-1142.90676864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5624120828438756</v>
+        <v>0.6915651035548448</v>
       </c>
       <c r="T97">
-        <v>10.62208816690849</v>
+        <v>13.27761020863561</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0201573039941345</v>
+        <v>0.01994733207752893</v>
       </c>
       <c r="W97">
-        <v>0.2310469077181831</v>
+        <v>0.2310964190961187</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1007865199706725</v>
+        <v>0.09973666038764462</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2495151664744676</v>
+        <v>0.2514151664744677</v>
       </c>
       <c r="C98">
-        <v>-8963.128799036051</v>
+        <v>-9084.072548464032</v>
       </c>
       <c r="D98">
-        <v>1272.947200963949</v>
+        <v>1261.184451535969</v>
       </c>
       <c r="E98">
-        <v>7037.776</v>
+        <v>7146.957</v>
       </c>
       <c r="F98">
-        <v>10481.376</v>
+        <v>10590.557</v>
       </c>
       <c r="G98">
         <v>245.3</v>
@@ -9329,37 +9329,37 @@
         <v>246.5</v>
       </c>
       <c r="M98">
-        <v>2471.5084608</v>
+        <v>2497.2533406</v>
       </c>
       <c r="N98">
-        <v>-2225.0084608</v>
+        <v>-2250.7533406</v>
       </c>
       <c r="O98">
-        <v>-445.0016921600001</v>
+        <v>-450.1506681200001</v>
       </c>
       <c r="P98">
-        <v>-1780.00676864</v>
+        <v>-1800.60267248</v>
       </c>
       <c r="Q98">
-        <v>-1142.90676864</v>
+        <v>-1163.50267248</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6915651035548431</v>
+        <v>0.9068201380731241</v>
       </c>
       <c r="T98">
-        <v>13.27761020863558</v>
+        <v>17.70348027818077</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01994733207752893</v>
+        <v>0.01974168947879152</v>
       </c>
       <c r="W98">
-        <v>0.2310964190961187</v>
+        <v>0.231144909620901</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.09973666038764462</v>
+        <v>0.09870844739395757</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2514151664744677</v>
+        <v>0.2533151664744677</v>
       </c>
       <c r="C99">
-        <v>-9084.072548464032</v>
+        <v>-9204.800899429403</v>
       </c>
       <c r="D99">
-        <v>1261.184451535969</v>
+        <v>1249.637100570596</v>
       </c>
       <c r="E99">
-        <v>7146.957</v>
+        <v>7256.137999999999</v>
       </c>
       <c r="F99">
-        <v>10590.557</v>
+        <v>10699.738</v>
       </c>
       <c r="G99">
         <v>245.3</v>
@@ -9411,37 +9411,37 @@
         <v>246.5</v>
       </c>
       <c r="M99">
-        <v>2497.2533406</v>
+        <v>2522.9982204</v>
       </c>
       <c r="N99">
-        <v>-2250.7533406</v>
+        <v>-2276.4982204</v>
       </c>
       <c r="O99">
-        <v>-450.1506681200001</v>
+        <v>-455.29964408</v>
       </c>
       <c r="P99">
-        <v>-1800.60267248</v>
+        <v>-1821.19857632</v>
       </c>
       <c r="Q99">
-        <v>-1163.50267248</v>
+        <v>-1184.09857632</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9068201380731241</v>
+        <v>1.337330207109686</v>
       </c>
       <c r="T99">
-        <v>17.70348027818077</v>
+        <v>26.55522041727115</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01974168947879152</v>
+        <v>0.01954024366778345</v>
       </c>
       <c r="W99">
-        <v>0.231144909620901</v>
+        <v>0.2311924105431367</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.09870844739395757</v>
+        <v>0.09770121833891721</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2533151664744677</v>
+        <v>0.2552151664744677</v>
       </c>
       <c r="C100">
-        <v>-9204.800899429403</v>
+        <v>-9325.319714789466</v>
       </c>
       <c r="D100">
-        <v>1249.637100570596</v>
+        <v>1238.299285210534</v>
       </c>
       <c r="E100">
-        <v>7256.137999999999</v>
+        <v>7365.319</v>
       </c>
       <c r="F100">
-        <v>10699.738</v>
+        <v>10808.919</v>
       </c>
       <c r="G100">
         <v>245.3</v>
@@ -9493,37 +9493,37 @@
         <v>246.5</v>
       </c>
       <c r="M100">
-        <v>2522.9982204</v>
+        <v>2548.7431002</v>
       </c>
       <c r="N100">
-        <v>-2276.4982204</v>
+        <v>-2302.2431002</v>
       </c>
       <c r="O100">
-        <v>-455.29964408</v>
+        <v>-460.4486200400001</v>
       </c>
       <c r="P100">
-        <v>-1821.19857632</v>
+        <v>-1841.79448016</v>
       </c>
       <c r="Q100">
-        <v>-1184.09857632</v>
+        <v>-1204.69448016</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.337330207109686</v>
+        <v>2.628860414219373</v>
       </c>
       <c r="T100">
-        <v>26.55522041727115</v>
+        <v>53.11044083454231</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01954024366778345</v>
+        <v>0.01934286746911897</v>
       </c>
       <c r="W100">
-        <v>0.2311924105431367</v>
+        <v>0.2312389518507817</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.09770121833891721</v>
+        <v>0.09671433734559487</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2552151664744677</v>
-      </c>
-      <c r="C101">
-        <v>-9325.319714789466</v>
-      </c>
-      <c r="D101">
-        <v>1238.299285210534</v>
-      </c>
-      <c r="E101">
-        <v>7365.319</v>
-      </c>
-      <c r="F101">
-        <v>10808.919</v>
-      </c>
-      <c r="G101">
-        <v>245.3</v>
-      </c>
-      <c r="H101">
-        <v>7474.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>883.6</v>
-      </c>
-      <c r="K101">
-        <v>637.1</v>
-      </c>
-      <c r="L101">
-        <v>246.5</v>
-      </c>
-      <c r="M101">
-        <v>2548.7431002</v>
-      </c>
-      <c r="N101">
-        <v>-2302.2431002</v>
-      </c>
-      <c r="O101">
-        <v>-460.4486200400001</v>
-      </c>
-      <c r="P101">
-        <v>-1841.79448016</v>
-      </c>
-      <c r="Q101">
-        <v>-1204.69448016</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.628860414219373</v>
-      </c>
-      <c r="T101">
-        <v>53.11044083454231</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01934286746911897</v>
-      </c>
-      <c r="W101">
-        <v>0.2312389518507817</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.09671433734559487</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
